--- a/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled_with_mdf.xlsx
+++ b/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled_with_mdf.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
   <si>
     <t xml:space="preserve">instrument</t>
   </si>
@@ -158,13 +158,22 @@
     <t xml:space="preserve">n_meas_pts</t>
   </si>
   <si>
+    <t xml:space="preserve">dt_s</t>
+  </si>
+  <si>
+    <t xml:space="preserve">t_sec</t>
+  </si>
+  <si>
     <t xml:space="preserve">flat_sd_CO2</t>
   </si>
   <si>
     <t xml:space="preserve">flat_sd_CH4</t>
   </si>
   <si>
-    <t xml:space="preserve">t_sec</t>
+    <t xml:space="preserve">mad_sd_CO2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">mad_sd_CH4</t>
   </si>
   <si>
     <t xml:space="preserve">CO2_MDF_goflux</t>
@@ -1052,19 +1061,28 @@
       <c r="CI1" t="s">
         <v>86</v>
       </c>
+      <c r="CJ1" t="s">
+        <v>87</v>
+      </c>
+      <c r="CK1" t="s">
+        <v>88</v>
+      </c>
+      <c r="CL1" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B2" t="s">
-        <v>88</v>
+        <v>91</v>
       </c>
       <c r="C2" t="s">
-        <v>89</v>
+        <v>92</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E2" t="n">
         <v>12.9</v>
@@ -1075,16 +1093,16 @@
       </c>
       <c r="H2"/>
       <c r="I2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="J2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="K2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="L2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="M2" t="n">
         <v>300</v>
@@ -1093,10 +1111,10 @@
         <v>1.14173417378919</v>
       </c>
       <c r="O2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q2" t="n">
         <v>1.09028443267916</v>
@@ -1120,10 +1138,10 @@
         <v>1.12969676375376</v>
       </c>
       <c r="X2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z2" t="n">
         <v>48</v>
@@ -1141,10 +1159,10 @@
         <v>-0.00484885854885949</v>
       </c>
       <c r="AE2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AF2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AG2" t="n">
         <v>-0.00403629265498706</v>
@@ -1168,10 +1186,10 @@
         <v>1.6590185751789</v>
       </c>
       <c r="AN2" t="s">
-        <v>100</v>
+        <v>103</v>
       </c>
       <c r="AO2" t="s">
-        <v>101</v>
+        <v>104</v>
       </c>
       <c r="AP2" t="n">
         <v>48</v>
@@ -1195,64 +1213,64 @@
         <v>48</v>
       </c>
       <c r="AW2" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX2" t="n">
+        <v>239</v>
+      </c>
+      <c r="AY2" t="n">
         <v>1.10388215394272</v>
       </c>
-      <c r="AX2" t="n">
+      <c r="AZ2" t="n">
         <v>1.24063893013517</v>
       </c>
-      <c r="AY2" t="n">
-        <v>48</v>
-      </c>
-      <c r="AZ2" t="n">
-        <v>0.0169876847148722</v>
-      </c>
       <c r="BA2" t="n">
-        <v>0.0436826178382427</v>
+        <v>1.04228663609991</v>
       </c>
       <c r="BB2" t="n">
-        <v>0.138008533048349</v>
+        <v>1.40029850566019</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.155106012158172</v>
+        <v>0.00341175257871909</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.105011521517088</v>
+        <v>0.00877307805956339</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.118021096039557</v>
+        <v>0.0261706032242944</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0881284469518497</v>
+        <v>0.0351598642042769</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.0990464260612465</v>
+        <v>0.0199133691439236</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.266547745086996</v>
+        <v>0.0267533518027599</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.652361021305115</v>
+        <v>0.0167118261965884</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.199676251919299</v>
+        <v>0.0224521205965961</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.488696700810343</v>
+        <v>0.053532601523748</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.166520618259721</v>
+        <v>0.131018113065462</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.407550101618064</v>
-      </c>
-      <c r="BN2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BO2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BP2" t="b">
-        <v>0</v>
+        <v>0.0401023434817001</v>
+      </c>
+      <c r="BN2" t="n">
+        <v>0.0981482913761359</v>
+      </c>
+      <c r="BO2" t="n">
+        <v>0.0334434714496511</v>
+      </c>
+      <c r="BP2" t="n">
+        <v>0.0818510664337534</v>
       </c>
       <c r="BQ2" t="b">
         <v>0</v>
@@ -1273,13 +1291,13 @@
         <v>0</v>
       </c>
       <c r="BW2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BY2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ2" t="b">
         <v>1</v>
@@ -1299,31 +1317,40 @@
       <c r="CE2" t="b">
         <v>1</v>
       </c>
-      <c r="CF2" t="n">
+      <c r="CF2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CI2" t="n">
         <v>-0.0160211732658191</v>
       </c>
-      <c r="CG2" t="n">
+      <c r="CJ2" t="n">
         <v>0.998747896186046</v>
       </c>
-      <c r="CH2" t="n">
-        <v>0.080927644909931</v>
-      </c>
-      <c r="CI2" t="n">
-        <v>0.0599159725240499</v>
+      <c r="CK2" t="n">
+        <v>0.0162532508605719</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>0.298331613192665</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B3" t="s">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="C3" t="s">
-        <v>103</v>
+        <v>106</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E3" t="n">
         <v>12.9</v>
@@ -1336,16 +1363,16 @@
       </c>
       <c r="H3"/>
       <c r="I3" t="s">
-        <v>104</v>
+        <v>107</v>
       </c>
       <c r="J3" t="s">
-        <v>105</v>
+        <v>108</v>
       </c>
       <c r="K3" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
       <c r="L3" t="s">
-        <v>107</v>
+        <v>110</v>
       </c>
       <c r="M3" t="n">
         <v>300</v>
@@ -1354,10 +1381,10 @@
         <v>1.3307836151745</v>
       </c>
       <c r="O3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q3" t="n">
         <v>1.27234696475888</v>
@@ -1381,10 +1408,10 @@
         <v>0.899074238592826</v>
       </c>
       <c r="X3" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z3" t="n">
         <v>77</v>
@@ -1402,10 +1429,10 @@
         <v>0.046013949999614</v>
       </c>
       <c r="AE3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AF3" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG3" t="n">
         <v>0.0387741109187982</v>
@@ -1429,10 +1456,10 @@
         <v>1.20687400068568</v>
       </c>
       <c r="AN3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AO3" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AP3" t="n">
         <v>77</v>
@@ -1456,64 +1483,64 @@
         <v>77</v>
       </c>
       <c r="AW3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX3" t="n">
+        <v>383</v>
+      </c>
+      <c r="AY3" t="n">
         <v>1.10388215394272</v>
       </c>
-      <c r="AX3" t="n">
+      <c r="AZ3" t="n">
         <v>1.24063893013517</v>
       </c>
-      <c r="AY3" t="n">
-        <v>77</v>
-      </c>
-      <c r="AZ3" t="n">
-        <v>0.0105909502488075</v>
-      </c>
       <c r="BA3" t="n">
-        <v>0.027233872068362</v>
+        <v>1.04228663609991</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.0860412429332613</v>
+        <v>1.40029850566019</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.0967006443567896</v>
+        <v>0.00212925109440776</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.065469298412713</v>
+        <v>0.00547521709990568</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0735801009639868</v>
+        <v>0.0163328917531181</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0549435672275326</v>
+        <v>0.0219430271125616</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0617503673009946</v>
+        <v>0.0124277954115196</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.148821568610144</v>
+        <v>0.0166965810945439</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.273820471546098</v>
+        <v>0.0104297346884391</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.112171648428468</v>
+        <v>0.0140122125649644</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.206387380227442</v>
+        <v>0.0299197409477313</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0937770731711071</v>
+        <v>0.0550500686920354</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.172542747907679</v>
-      </c>
-      <c r="BN3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BO3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BP3" t="b">
-        <v>0</v>
+        <v>0.0225514802323552</v>
+      </c>
+      <c r="BN3" t="n">
+        <v>0.0414930242232717</v>
+      </c>
+      <c r="BO3" t="n">
+        <v>0.0188533541362278</v>
+      </c>
+      <c r="BP3" t="n">
+        <v>0.0346887508848337</v>
       </c>
       <c r="BQ3" t="b">
         <v>0</v>
@@ -1537,22 +1564,22 @@
         <v>0</v>
       </c>
       <c r="BX3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BY3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD3" t="b">
         <v>1</v>
@@ -1560,31 +1587,40 @@
       <c r="CE3" t="b">
         <v>0</v>
       </c>
-      <c r="CF3" t="n">
+      <c r="CF3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG3" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI3" t="n">
         <v>0.695258815852541</v>
       </c>
-      <c r="CG3" t="n">
+      <c r="CJ3" t="n">
         <v>0.99977497116895</v>
       </c>
-      <c r="CH3" t="n">
-        <v>0.0345342698771411</v>
-      </c>
-      <c r="CI3" t="n">
-        <v>1.33241415449966</v>
+      <c r="CK3" t="n">
+        <v>0.00694292109801531</v>
+      </c>
+      <c r="CL3" t="n">
+        <v>6.62746261264117</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B4" t="s">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E4" t="n">
         <v>10.6</v>
@@ -1597,16 +1633,16 @@
       </c>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>111</v>
+        <v>114</v>
       </c>
       <c r="J4" t="s">
-        <v>112</v>
+        <v>115</v>
       </c>
       <c r="K4" t="s">
-        <v>113</v>
+        <v>116</v>
       </c>
       <c r="L4" t="s">
-        <v>114</v>
+        <v>117</v>
       </c>
       <c r="M4" t="n">
         <v>600</v>
@@ -1615,10 +1651,10 @@
         <v>1.1261297916822</v>
       </c>
       <c r="O4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q4" t="n">
         <v>1.01572817524315</v>
@@ -1642,10 +1678,10 @@
         <v>1.40769764878489</v>
       </c>
       <c r="X4" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z4" t="n">
         <v>149</v>
@@ -1663,10 +1699,10 @@
         <v>0.0314898091802709</v>
       </c>
       <c r="AE4" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AF4" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG4" t="n">
         <v>0.0272394087536914</v>
@@ -1690,10 +1726,10 @@
         <v>1.75863641061905</v>
       </c>
       <c r="AN4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AO4" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AP4" t="n">
         <v>149</v>
@@ -1717,64 +1753,64 @@
         <v>149</v>
       </c>
       <c r="AW4" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX4" t="n">
+        <v>741</v>
+      </c>
+      <c r="AY4" t="n">
         <v>1.10388215394272</v>
       </c>
-      <c r="AX4" t="n">
+      <c r="AZ4" t="n">
         <v>1.24063893013517</v>
       </c>
-      <c r="AY4" t="n">
-        <v>149</v>
-      </c>
-      <c r="AZ4" t="n">
-        <v>0.00548708239664158</v>
-      </c>
       <c r="BA4" t="n">
-        <v>0.0141096404485069</v>
+        <v>1.04228663609991</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.0445772455155683</v>
+        <v>1.40029850566019</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0500997918910802</v>
+        <v>0.00110334045492523</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.0339190937924878</v>
+        <v>0.00283716116980773</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.0381212324916797</v>
+        <v>0.00846341714439373</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0284658008450974</v>
+        <v>0.0113704905825324</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.0319923468096351</v>
+        <v>0.00643986492672325</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.11138257299646</v>
+        <v>0.00865187456234416</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.165465728935058</v>
+        <v>0.00540450501404703</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.0843464656044522</v>
+        <v>0.00726088201928903</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.125301912488411</v>
+        <v>0.0223967656902464</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0706482759480357</v>
+        <v>0.0332717862500995</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.104952401109628</v>
-      </c>
-      <c r="BN4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BO4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BP4" t="b">
-        <v>0</v>
+        <v>0.0169603554319344</v>
+      </c>
+      <c r="BN4" t="n">
+        <v>0.0251956612156184</v>
+      </c>
+      <c r="BO4" t="n">
+        <v>0.0142059286319262</v>
+      </c>
+      <c r="BP4" t="n">
+        <v>0.0211037891569967</v>
       </c>
       <c r="BQ4" t="b">
         <v>0</v>
@@ -1798,22 +1834,22 @@
         <v>0</v>
       </c>
       <c r="BX4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BY4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD4" t="b">
         <v>1</v>
@@ -1821,31 +1857,40 @@
       <c r="CE4" t="b">
         <v>0</v>
       </c>
-      <c r="CF4" t="n">
+      <c r="CF4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG4" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI4" t="n">
         <v>0.665931303103025</v>
       </c>
-      <c r="CG4" t="n">
+      <c r="CJ4" t="n">
         <v>0.999769549580697</v>
       </c>
-      <c r="CH4" t="n">
-        <v>0.0211348042636478</v>
-      </c>
-      <c r="CI4" t="n">
-        <v>1.48995035806571</v>
+      <c r="CK4" t="n">
+        <v>0.00424977845517345</v>
+      </c>
+      <c r="CL4" t="n">
+        <v>7.40975312299795</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B5" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C5" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E5" t="n">
         <v>12.9</v>
@@ -1858,16 +1903,16 @@
       </c>
       <c r="H5"/>
       <c r="I5" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="J5" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="K5" t="s">
-        <v>119</v>
+        <v>122</v>
       </c>
       <c r="L5" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="M5" t="n">
         <v>300</v>
@@ -1876,10 +1921,10 @@
         <v>1.20842158337</v>
       </c>
       <c r="O5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q5" t="n">
         <v>1.12550151487279</v>
@@ -1903,10 +1948,10 @@
         <v>2.27421231286376</v>
       </c>
       <c r="X5" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z5" t="n">
         <v>69</v>
@@ -1924,10 +1969,10 @@
         <v>0.0384520122066485</v>
       </c>
       <c r="AE5" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AF5" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG5" t="n">
         <v>0.0384203355769582</v>
@@ -1951,10 +1996,10 @@
         <v>1.61678069534197</v>
       </c>
       <c r="AN5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AO5" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AP5" t="n">
         <v>69</v>
@@ -1978,64 +2023,64 @@
         <v>69</v>
       </c>
       <c r="AW5" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX5" t="n">
+        <v>343</v>
+      </c>
+      <c r="AY5" t="n">
         <v>1.10388215394272</v>
       </c>
-      <c r="AX5" t="n">
+      <c r="AZ5" t="n">
         <v>1.24063893013517</v>
       </c>
-      <c r="AY5" t="n">
-        <v>69</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>0.0118306464064284</v>
-      </c>
       <c r="BA5" t="n">
-        <v>0.0304216621879589</v>
+        <v>1.04228663609991</v>
       </c>
       <c r="BB5" t="n">
-        <v>0.0961125770208999</v>
+        <v>1.40029850566019</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.108019686976415</v>
+        <v>0.00237992595347978</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.073132636996852</v>
+        <v>0.00611980959466228</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0821928284624179</v>
+        <v>0.0182557487375312</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0613748437020522</v>
+        <v>0.0245263603997917</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0689783960686066</v>
+        <v>0.0138909088374281</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.291497849523514</v>
+        <v>0.0186622549053272</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.342222766508585</v>
+        <v>0.011657618182335</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.21945829162363</v>
+        <v>0.0156618580291535</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.257647265032835</v>
+        <v>0.0586395090878207</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.183385014514273</v>
+        <v>0.0688436469069749</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.215296706668256</v>
-      </c>
-      <c r="BN5" t="b">
-        <v>0</v>
-      </c>
-      <c r="BO5" t="b">
-        <v>0</v>
-      </c>
-      <c r="BP5" t="b">
-        <v>0</v>
+        <v>0.0441475863616049</v>
+      </c>
+      <c r="BN5" t="n">
+        <v>0.0518299162894042</v>
+      </c>
+      <c r="BO5" t="n">
+        <v>0.0368908629780899</v>
+      </c>
+      <c r="BP5" t="n">
+        <v>0.0433104162102322</v>
       </c>
       <c r="BQ5" t="b">
         <v>0</v>
@@ -2059,54 +2104,63 @@
         <v>0</v>
       </c>
       <c r="BX5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BY5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD5" t="b">
         <v>1</v>
       </c>
       <c r="CE5" t="b">
-        <v>0</v>
-      </c>
-      <c r="CF5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CF5" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG5" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH5" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI5" t="n">
         <v>0.496975719496566</v>
       </c>
-      <c r="CG5" t="n">
+      <c r="CJ5" t="n">
         <v>0.997707251307285</v>
       </c>
-      <c r="CH5" t="n">
-        <v>0.0430270852846958</v>
-      </c>
-      <c r="CI5" t="n">
-        <v>0.893669927958735</v>
+      <c r="CK5" t="n">
+        <v>0.00865559441587176</v>
+      </c>
+      <c r="CL5" t="n">
+        <v>4.44244616362096</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>124</v>
       </c>
       <c r="C6" t="s">
-        <v>122</v>
+        <v>125</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E6" t="n">
         <v>11.5</v>
@@ -2118,19 +2172,19 @@
         <v>9.4</v>
       </c>
       <c r="H6" t="s">
-        <v>123</v>
+        <v>126</v>
       </c>
       <c r="I6" t="s">
-        <v>124</v>
+        <v>127</v>
       </c>
       <c r="J6" t="s">
-        <v>125</v>
+        <v>128</v>
       </c>
       <c r="K6" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="L6" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="M6" t="n">
         <v>600</v>
@@ -2139,10 +2193,10 @@
         <v>1.32386833098952</v>
       </c>
       <c r="O6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="Q6" t="n">
         <v>1.30314854895781</v>
@@ -2166,10 +2220,10 @@
         <v>0.704654629061883</v>
       </c>
       <c r="X6" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z6" t="n">
         <v>62</v>
@@ -2187,10 +2241,10 @@
         <v>0.353678991732009</v>
       </c>
       <c r="AE6" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AF6" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG6" t="n">
         <v>0.330400946519775</v>
@@ -2214,10 +2268,10 @@
         <v>1.22995859003021</v>
       </c>
       <c r="AN6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AO6" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AP6" t="n">
         <v>62</v>
@@ -2241,64 +2295,64 @@
         <v>62</v>
       </c>
       <c r="AW6" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX6" t="n">
+        <v>308</v>
+      </c>
+      <c r="AY6" t="n">
         <v>1.10388215394272</v>
       </c>
-      <c r="AX6" t="n">
+      <c r="AZ6" t="n">
         <v>1.24063893013517</v>
       </c>
-      <c r="AY6" t="n">
-        <v>62</v>
-      </c>
-      <c r="AZ6" t="n">
-        <v>0.0131755187787025</v>
-      </c>
       <c r="BA6" t="n">
-        <v>0.0338799054309493</v>
+        <v>1.04228663609991</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.107038366282359</v>
+        <v>1.40029850566019</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.120299040756893</v>
+        <v>0.00265221481908947</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0814461356536262</v>
+        <v>0.00681998096337291</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0915362624896662</v>
+        <v>0.0203444007425777</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0683517517096044</v>
+        <v>0.0273324371355108</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0768196530861471</v>
+        <v>0.0154801766901109</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.146280124345726</v>
+        <v>0.020797415543607</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.37329094553287</v>
+        <v>0.0129913738086131</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.109989730776377</v>
+        <v>0.0174537413227757</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.280681813637105</v>
+        <v>0.0294459990566072</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0918634299604868</v>
+        <v>0.0751429825423309</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.234425468143544</v>
-      </c>
-      <c r="BN6" t="b">
-        <v>0</v>
-      </c>
-      <c r="BO6" t="b">
-        <v>0</v>
-      </c>
-      <c r="BP6" t="b">
-        <v>0</v>
+        <v>0.0221407899614785</v>
+      </c>
+      <c r="BN6" t="n">
+        <v>0.0565008845633134</v>
+      </c>
+      <c r="BO6" t="n">
+        <v>0.0184919891478902</v>
+      </c>
+      <c r="BP6" t="n">
+        <v>0.0471895422886355</v>
       </c>
       <c r="BQ6" t="b">
         <v>0</v>
@@ -2331,7 +2385,7 @@
         <v>0</v>
       </c>
       <c r="CA6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB6" t="b">
         <v>0</v>
@@ -2340,36 +2394,45 @@
         <v>0</v>
       </c>
       <c r="CD6" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE6" t="b">
         <v>0</v>
       </c>
-      <c r="CF6" t="n">
+      <c r="CF6" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH6" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI6" t="n">
         <v>0.990407805013714</v>
       </c>
-      <c r="CG6" t="n">
+      <c r="CJ6" t="n">
         <v>0.999795764899988</v>
       </c>
-      <c r="CH6" t="n">
-        <v>0.0467733372081004</v>
-      </c>
-      <c r="CI6" t="n">
-        <v>7.56155136330015</v>
+      <c r="CK6" t="n">
+        <v>0.00941541203539683</v>
+      </c>
+      <c r="CL6" t="n">
+        <v>37.5638358047814</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B7" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="C7" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E7"/>
       <c r="F7"/>
@@ -2378,16 +2441,16 @@
       </c>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="J7" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="K7" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="L7" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="M7" t="n">
         <v>600</v>
@@ -2396,10 +2459,10 @@
         <v>1.34106207568664</v>
       </c>
       <c r="O7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q7" t="n">
         <v>1.31933987276378</v>
@@ -2423,10 +2486,10 @@
         <v>0.971891773133964</v>
       </c>
       <c r="X7" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z7" t="n">
         <v>117</v>
@@ -2444,10 +2507,10 @@
         <v>0.396629714787707</v>
       </c>
       <c r="AE7" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AF7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AG7" t="n">
         <v>0.369704402424142</v>
@@ -2471,10 +2534,10 @@
         <v>1.14932531698564</v>
       </c>
       <c r="AN7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AO7" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AP7" t="n">
         <v>117</v>
@@ -2498,64 +2561,64 @@
         <v>117</v>
       </c>
       <c r="AW7" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX7" t="n">
+        <v>582</v>
+      </c>
+      <c r="AY7" t="n">
         <v>1.10388215394272</v>
       </c>
-      <c r="AX7" t="n">
+      <c r="AZ7" t="n">
         <v>1.24063893013517</v>
       </c>
-      <c r="AY7" t="n">
-        <v>117</v>
-      </c>
-      <c r="AZ7" t="n">
-        <v>0.00697950251157923</v>
-      </c>
       <c r="BA7" t="n">
-        <v>0.0179472921726323</v>
+        <v>1.04228663609991</v>
       </c>
       <c r="BB7" t="n">
-        <v>0.0567017176971174</v>
+        <v>1.40029850566019</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.0637263299613308</v>
+        <v>0.00140309586572985</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0431446774810704</v>
+        <v>0.00360796079759103</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0484897471346564</v>
+        <v>0.0107627573630939</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0362081547406821</v>
+        <v>0.0144596241862196</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.040693878598548</v>
+        <v>0.00818944670632634</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.109775651159509</v>
+        <v>0.011002414871175</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.17340174401312</v>
+        <v>0.0068728003289243</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0830175718645747</v>
+        <v>0.00923351763033742</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.131134651382159</v>
+        <v>0.022068301006293</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0694972716478955</v>
+        <v>0.0348591134871735</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.109777969710132</v>
-      </c>
-      <c r="BN7" t="b">
-        <v>0</v>
-      </c>
-      <c r="BO7" t="b">
-        <v>0</v>
-      </c>
-      <c r="BP7" t="b">
-        <v>0</v>
+        <v>0.0166890994985485</v>
+      </c>
+      <c r="BN7" t="n">
+        <v>0.0263621206386815</v>
+      </c>
+      <c r="BO7" t="n">
+        <v>0.013971101001381</v>
+      </c>
+      <c r="BP7" t="n">
+        <v>0.0220687671066761</v>
       </c>
       <c r="BQ7" t="b">
         <v>0</v>
@@ -2602,31 +2665,40 @@
       <c r="CE7" t="b">
         <v>0</v>
       </c>
-      <c r="CF7" t="n">
+      <c r="CF7" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH7" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI7" t="n">
         <v>0.998122550225431</v>
       </c>
-      <c r="CG7" t="n">
+      <c r="CJ7" t="n">
         <v>0.999894443336438</v>
       </c>
-      <c r="CH7" t="n">
-        <v>0.0220675404115027</v>
-      </c>
-      <c r="CI7" t="n">
-        <v>17.9734445883676</v>
+      <c r="CK7" t="n">
+        <v>0.00443625812396188</v>
+      </c>
+      <c r="CL7" t="n">
+        <v>89.4063653882902</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>137</v>
       </c>
       <c r="C8" t="s">
-        <v>135</v>
+        <v>138</v>
       </c>
       <c r="D8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E8" t="n">
         <v>11.4</v>
@@ -2639,16 +2711,16 @@
       </c>
       <c r="H8"/>
       <c r="I8" t="s">
-        <v>126</v>
+        <v>129</v>
       </c>
       <c r="J8" t="s">
-        <v>127</v>
+        <v>130</v>
       </c>
       <c r="K8" t="s">
-        <v>136</v>
+        <v>139</v>
       </c>
       <c r="L8" t="s">
-        <v>137</v>
+        <v>140</v>
       </c>
       <c r="M8" t="n">
         <v>600</v>
@@ -2657,10 +2729,10 @@
         <v>1.09834555739463</v>
       </c>
       <c r="O8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q8" t="n">
         <v>0.932800122520638</v>
@@ -2684,10 +2756,10 @@
         <v>1.1228647114697</v>
       </c>
       <c r="X8" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z8" t="n">
         <v>166</v>
@@ -2705,10 +2777,10 @@
         <v>0.0337112943119567</v>
       </c>
       <c r="AE8" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AF8" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG8" t="n">
         <v>0.0336412225079778</v>
@@ -2732,10 +2804,10 @@
         <v>1.38367415839523</v>
       </c>
       <c r="AN8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AO8" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AP8" t="n">
         <v>166</v>
@@ -2759,64 +2831,64 @@
         <v>166</v>
       </c>
       <c r="AW8" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX8" t="n">
+        <v>826</v>
+      </c>
+      <c r="AY8" t="n">
         <v>1.10388215394272</v>
       </c>
-      <c r="AX8" t="n">
+      <c r="AZ8" t="n">
         <v>1.24063893013517</v>
       </c>
-      <c r="AY8" t="n">
-        <v>166</v>
-      </c>
-      <c r="AZ8" t="n">
-        <v>0.00492132249443286</v>
-      </c>
       <c r="BA8" t="n">
-        <v>0.0126548292713988</v>
+        <v>1.04228663609991</v>
       </c>
       <c r="BB8" t="n">
-        <v>0.0399809926728813</v>
+        <v>1.40029850566019</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.0449341225404025</v>
+        <v>0.000989030912924763</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.0304217774046763</v>
+        <v>0.00254322234752082</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.0341906436636772</v>
+        <v>0.00758658050415642</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0255307604104444</v>
+        <v>0.0101924719890802</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.0286936926808899</v>
+        <v>0.00577267466189381</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.0609877326793533</v>
+        <v>0.00775551314076094</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.143252216155764</v>
+        <v>0.00484458129318898</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.0462071914551354</v>
+        <v>0.00650863180092774</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.108534655864042</v>
+        <v>0.0122566145578361</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0387108138564723</v>
+        <v>0.0287891862976474</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.0909266442694014</v>
-      </c>
-      <c r="BN8" t="b">
-        <v>0</v>
-      </c>
-      <c r="BO8" t="b">
-        <v>0</v>
-      </c>
-      <c r="BP8" t="b">
-        <v>0</v>
+        <v>0.00928619101882867</v>
+      </c>
+      <c r="BN8" t="n">
+        <v>0.0218120494835727</v>
+      </c>
+      <c r="BO8" t="n">
+        <v>0.0077796550849569</v>
+      </c>
+      <c r="BP8" t="n">
+        <v>0.0182733934003882</v>
       </c>
       <c r="BQ8" t="b">
         <v>0</v>
@@ -2840,54 +2912,63 @@
         <v>0</v>
       </c>
       <c r="BX8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BY8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ8" t="b">
         <v>0</v>
       </c>
       <c r="CA8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD8" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE8" t="b">
         <v>0</v>
       </c>
-      <c r="CF8" t="n">
+      <c r="CF8" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH8" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI8" t="n">
         <v>0.859492457974167</v>
       </c>
-      <c r="CG8" t="n">
+      <c r="CJ8" t="n">
         <v>0.999860422432155</v>
       </c>
-      <c r="CH8" t="n">
-        <v>0.0183224031950001</v>
-      </c>
-      <c r="CI8" t="n">
-        <v>1.8398947972696</v>
+      <c r="CK8" t="n">
+        <v>0.00368222630795402</v>
+      </c>
+      <c r="CL8" t="n">
+        <v>9.15513917195598</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B9" t="s">
-        <v>138</v>
+        <v>141</v>
       </c>
       <c r="C9" t="s">
-        <v>139</v>
+        <v>142</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E9" t="n">
         <v>11.3</v>
@@ -2900,16 +2981,16 @@
       </c>
       <c r="H9"/>
       <c r="I9" t="s">
-        <v>140</v>
+        <v>143</v>
       </c>
       <c r="J9" t="s">
-        <v>141</v>
+        <v>144</v>
       </c>
       <c r="K9" t="s">
-        <v>142</v>
+        <v>145</v>
       </c>
       <c r="L9" t="s">
-        <v>143</v>
+        <v>146</v>
       </c>
       <c r="M9" t="n">
         <v>900</v>
@@ -2918,10 +2999,10 @@
         <v>1.25398474563604</v>
       </c>
       <c r="O9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q9" t="n">
         <v>1.10063846684457</v>
@@ -2945,10 +3026,10 @@
         <v>1.17849683682608</v>
       </c>
       <c r="X9" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z9" t="n">
         <v>192</v>
@@ -2966,10 +3047,10 @@
         <v>0.0765684447151247</v>
       </c>
       <c r="AE9" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AF9" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG9" t="n">
         <v>0.0760943600684935</v>
@@ -2993,10 +3074,10 @@
         <v>1.56049523863239</v>
       </c>
       <c r="AN9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AO9" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="AP9" t="n">
         <v>192</v>
@@ -3020,64 +3101,64 @@
         <v>192</v>
       </c>
       <c r="AW9" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX9" t="n">
+        <v>954</v>
+      </c>
+      <c r="AY9" t="n">
         <v>1.10388215394272</v>
       </c>
-      <c r="AX9" t="n">
+      <c r="AZ9" t="n">
         <v>1.24063893013517</v>
       </c>
-      <c r="AY9" t="n">
-        <v>192</v>
-      </c>
-      <c r="AZ9" t="n">
-        <v>0.00425843595209661</v>
-      </c>
       <c r="BA9" t="n">
-        <v>0.0109502638768199</v>
+        <v>1.04228663609991</v>
       </c>
       <c r="BB9" t="n">
-        <v>0.0345956796758001</v>
+        <v>1.40029850566019</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.0388816386486405</v>
+        <v>0.000857043713629507</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.0263240604071982</v>
+        <v>0.00220382669219016</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.0295852723261751</v>
+        <v>0.00657414348132317</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.0220918479004759</v>
+        <v>0.00883227604964717</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0248287432187056</v>
+        <v>0.0050023052516871</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.0568501845799588</v>
+        <v>0.00672053188267315</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.109670233856289</v>
+        <v>0.0041980669039114</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.0430978645496238</v>
+        <v>0.00564004814856435</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0831405019840541</v>
+        <v>0.0114415465821301</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0361145757202873</v>
+        <v>0.0220719967509512</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.0696689728296996</v>
-      </c>
-      <c r="BN9" t="b">
-        <v>0</v>
-      </c>
-      <c r="BO9" t="b">
-        <v>0</v>
-      </c>
-      <c r="BP9" t="b">
-        <v>0</v>
+        <v>0.00867378406030165</v>
+      </c>
+      <c r="BN9" t="n">
+        <v>0.0167326796445895</v>
+      </c>
+      <c r="BO9" t="n">
+        <v>0.00726834228332826</v>
+      </c>
+      <c r="BP9" t="n">
+        <v>0.0140214284940276</v>
       </c>
       <c r="BQ9" t="b">
         <v>0</v>
@@ -3110,61 +3191,70 @@
         <v>0</v>
       </c>
       <c r="CA9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC9" t="b">
         <v>0</v>
       </c>
       <c r="CD9" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE9" t="b">
         <v>0</v>
       </c>
-      <c r="CF9" t="n">
+      <c r="CF9" t="b">
+        <v>0</v>
+      </c>
+      <c r="CG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="CH9" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI9" t="n">
         <v>0.97052787072339</v>
       </c>
-      <c r="CG9" t="n">
+      <c r="CJ9" t="n">
         <v>0.9999173464781</v>
       </c>
-      <c r="CH9" t="n">
-        <v>0.0140497362289817</v>
-      </c>
-      <c r="CI9" t="n">
-        <v>5.44981368099848</v>
+      <c r="CK9" t="n">
+        <v>0.00282761986998374</v>
+      </c>
+      <c r="CL9" t="n">
+        <v>27.0787617274612</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>90</v>
       </c>
       <c r="B10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="C10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="J10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="K10" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="L10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="M10" t="n">
         <v>300</v>
@@ -3173,10 +3263,10 @@
         <v>1.34102040741186</v>
       </c>
       <c r="O10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="P10" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="Q10" t="n">
         <v>1.26070021803685</v>
@@ -3200,10 +3290,10 @@
         <v>1.13993468094949</v>
       </c>
       <c r="X10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="Y10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="Z10" t="n">
         <v>70</v>
@@ -3221,10 +3311,10 @@
         <v>0.00965562852738834</v>
       </c>
       <c r="AE10" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="AF10" t="s">
-        <v>108</v>
+        <v>111</v>
       </c>
       <c r="AG10" t="n">
         <v>0.00966301603762399</v>
@@ -3248,10 +3338,10 @@
         <v>3.7919252851978</v>
       </c>
       <c r="AN10" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="AO10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AP10" t="n">
         <v>70</v>
@@ -3275,94 +3365,94 @@
         <v>70</v>
       </c>
       <c r="AW10" t="n">
+        <v>5</v>
+      </c>
+      <c r="AX10" t="n">
+        <v>575</v>
+      </c>
+      <c r="AY10" t="n">
         <v>1.10388215394272</v>
       </c>
-      <c r="AX10" t="n">
+      <c r="AZ10" t="n">
         <v>1.24063893013517</v>
       </c>
-      <c r="AY10" t="n">
-        <v>70</v>
-      </c>
-      <c r="AZ10" t="n">
-        <v>0.0116263382198069</v>
-      </c>
       <c r="BA10" t="n">
-        <v>0.0298962982795033</v>
+        <v>1.04228663609991</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0944527703080563</v>
+        <v>1.40029850566019</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.106154251597196</v>
+        <v>0.00141538030501996</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0718696801021582</v>
+        <v>0.00363954935576562</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0807734074807096</v>
+        <v>0.0108569878733894</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0603149368643213</v>
+        <v>0.0145862216481693</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0677871804297734</v>
+        <v>0.0082611472674503</v>
       </c>
       <c r="BH10" t="n">
-        <v>2.6200523480139</v>
+        <v>0.0110987436401713</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.638007459673722</v>
+        <v>0.00693297333666805</v>
       </c>
       <c r="BJ10" t="n">
-        <v>1.9728576107294</v>
+        <v>0.00931435928167043</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.480409436656323</v>
+        <v>0.318962894540822</v>
       </c>
       <c r="BL10" t="n">
-        <v>1.648676465864</v>
+        <v>0.0776704733515835</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.401468270130976</v>
-      </c>
-      <c r="BN10" t="b">
-        <v>0</v>
-      </c>
-      <c r="BO10" t="b">
-        <v>0</v>
-      </c>
-      <c r="BP10" t="b">
-        <v>0</v>
+        <v>0.24017397000184</v>
+      </c>
+      <c r="BN10" t="n">
+        <v>0.0584846270712045</v>
+      </c>
+      <c r="BO10" t="n">
+        <v>0.200708439322574</v>
+      </c>
+      <c r="BP10" t="n">
+        <v>0.0488743981029014</v>
       </c>
       <c r="BQ10" t="b">
         <v>0</v>
       </c>
       <c r="BR10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BT10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BU10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BV10" t="b">
         <v>0</v>
       </c>
       <c r="BW10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BX10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BY10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BZ10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA10" t="b">
         <v>1</v>
@@ -3371,7 +3461,7 @@
         <v>1</v>
       </c>
       <c r="CC10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CD10" t="b">
         <v>1</v>
@@ -3379,17 +3469,26 @@
       <c r="CE10" t="b">
         <v>1</v>
       </c>
-      <c r="CF10" t="n">
+      <c r="CF10" t="b">
+        <v>1</v>
+      </c>
+      <c r="CG10" t="b">
+        <v>1</v>
+      </c>
+      <c r="CH10" t="b">
+        <v>0</v>
+      </c>
+      <c r="CI10" t="n">
         <v>0.0305018423219471</v>
       </c>
-      <c r="CG10" t="n">
+      <c r="CJ10" t="n">
         <v>0.999884540341955</v>
       </c>
-      <c r="CH10" t="n">
-        <v>0.0802500486793828</v>
-      </c>
-      <c r="CI10" t="n">
-        <v>0.120319285611461</v>
+      <c r="CK10" t="n">
+        <v>0.00976957114357704</v>
+      </c>
+      <c r="CL10" t="n">
+        <v>0.98833698895129</v>
       </c>
     </row>
   </sheetData>

--- a/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled_with_mdf.xlsx
+++ b/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled_with_mdf.xlsx
@@ -1108,7 +1108,7 @@
         <v>300</v>
       </c>
       <c r="N2" t="n">
-        <v>1.14173417378919</v>
+        <v>1.12174549713261</v>
       </c>
       <c r="O2" t="s">
         <v>98</v>
@@ -1117,7 +1117,7 @@
         <v>99</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.09028443267916</v>
+        <v>1.07119650180274</v>
       </c>
       <c r="R2" t="n">
         <v>0.998592889197321</v>
@@ -1129,7 +1129,7 @@
         <v>1.1975836661462</v>
       </c>
       <c r="U2" t="n">
-        <v>1.14173417378919</v>
+        <v>1.12174549713261</v>
       </c>
       <c r="V2" t="n">
         <v>0.998747896186046</v>
@@ -1147,16 +1147,16 @@
         <v>48</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.32973961803961</v>
+        <v>2.28895217995805</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00198275712173584</v>
+        <v>0.00194804440847494</v>
       </c>
       <c r="AC2" t="n">
         <v>1.04718928342727</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.00484885854885949</v>
+        <v>-0.00476396815325628</v>
       </c>
       <c r="AE2" t="s">
         <v>98</v>
@@ -1165,7 +1165,7 @@
         <v>102</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.00403629265498706</v>
+        <v>-0.00396562808995602</v>
       </c>
       <c r="AH2" t="n">
         <v>-0.016477614613488</v>
@@ -1177,7 +1177,7 @@
         <v>1.65939118535001</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.00484885854885949</v>
+        <v>-0.00476396815325628</v>
       </c>
       <c r="AL2" t="n">
         <v>-0.0160211732658191</v>
@@ -1195,10 +1195,10 @@
         <v>48</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.32973961803961</v>
+        <v>2.28895217995805</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.0138792998521509</v>
+        <v>0.0136363108593246</v>
       </c>
       <c r="AS2" t="n">
         <v>1.20131491032209</v>
@@ -1231,46 +1231,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.00341175257871909</v>
+        <v>0.00335202202085907</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.00877307805956339</v>
+        <v>0.00861948519649475</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0261706032242944</v>
+        <v>0.0257124267610096</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0351598642042769</v>
+        <v>0.0345443100998252</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.0199133691439236</v>
+        <v>0.019564739921729</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0267533518027599</v>
+        <v>0.0262849729883723</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0167118261965884</v>
+        <v>0.0164192473302872</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.0224521205965961</v>
+        <v>0.022059044704534</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.053532601523748</v>
+        <v>0.0525953904924861</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.131018113065462</v>
+        <v>0.128724340348185</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0401023434817001</v>
+        <v>0.0394002599359597</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.0981482913761359</v>
+        <v>0.096429980314111</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0334434714496511</v>
+        <v>0.0328579667389861</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0818510664337534</v>
+        <v>0.0804180756916869</v>
       </c>
       <c r="BQ2" t="b">
         <v>0</v>
@@ -1333,7 +1333,7 @@
         <v>0.998747896186046</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.0162532508605719</v>
+        <v>0.0159687004078233</v>
       </c>
       <c r="CL2" t="n">
         <v>0.298331613192665</v>
@@ -1378,7 +1378,7 @@
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>1.3307836151745</v>
+        <v>1.30748519423355</v>
       </c>
       <c r="O3" t="s">
         <v>98</v>
@@ -1387,7 +1387,7 @@
         <v>99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.27234696475888</v>
+        <v>1.2500716114784</v>
       </c>
       <c r="R3" t="n">
         <v>0.999633472356177</v>
@@ -1399,7 +1399,7 @@
         <v>1.1474396140762</v>
       </c>
       <c r="U3" t="n">
-        <v>1.3307836151745</v>
+        <v>1.30748519423355</v>
       </c>
       <c r="V3" t="n">
         <v>0.99977497116895</v>
@@ -1417,16 +1417,16 @@
         <v>77</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.33000905473764</v>
+        <v>2.2892168995484</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.001229556229413</v>
+        <v>0.00120803002614691</v>
       </c>
       <c r="AC3" t="n">
         <v>1.04592823501308</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.046013949999614</v>
+        <v>0.0452083702163778</v>
       </c>
       <c r="AE3" t="s">
         <v>98</v>
@@ -1435,7 +1435,7 @@
         <v>111</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0387741109187982</v>
+        <v>0.0380952811319747</v>
       </c>
       <c r="AH3" t="n">
         <v>0.693680686527493</v>
@@ -1447,7 +1447,7 @@
         <v>1.20999491759047</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.046013949999614</v>
+        <v>0.0452083702163778</v>
       </c>
       <c r="AL3" t="n">
         <v>0.695258815852541</v>
@@ -1465,10 +1465,10 @@
         <v>77</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.33000905473764</v>
+        <v>2.2892168995484</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.00860689360589101</v>
+        <v>0.00845621018302839</v>
       </c>
       <c r="AS3" t="n">
         <v>1.18671837752715</v>
@@ -1501,46 +1501,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.00212925109440776</v>
+        <v>0.00209197366799462</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.00547521709990568</v>
+        <v>0.0053793608605576</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0163328917531181</v>
+        <v>0.0160469470037929</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0219430271125616</v>
+        <v>0.0215588640701574</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0124277954115196</v>
+        <v>0.0122102183347026</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0166965810945439</v>
+        <v>0.0164042691287369</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0104297346884391</v>
+        <v>0.0102471382495419</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0140122125649644</v>
+        <v>0.0137668966301046</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0299197409477313</v>
+        <v>0.0293959272254283</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0550500686920354</v>
+        <v>0.0540862909158513</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0225514802323552</v>
+        <v>0.0221566648218679</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.0414930242232717</v>
+        <v>0.0407665936199463</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0188533541362278</v>
+        <v>0.0185232829091659</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0346887508848337</v>
+        <v>0.0340814447001055</v>
       </c>
       <c r="BQ3" t="b">
         <v>0</v>
@@ -1603,10 +1603,10 @@
         <v>0.99977497116895</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.00694292109801531</v>
+        <v>0.00682136933223095</v>
       </c>
       <c r="CL3" t="n">
-        <v>6.62746261264117</v>
+        <v>6.62746261264118</v>
       </c>
     </row>
     <row r="4">
@@ -1648,7 +1648,7 @@
         <v>600</v>
       </c>
       <c r="N4" t="n">
-        <v>1.1261297916822</v>
+        <v>1.10641430554187</v>
       </c>
       <c r="O4" t="s">
         <v>98</v>
@@ -1657,7 +1657,7 @@
         <v>99</v>
       </c>
       <c r="Q4" t="n">
-        <v>1.01572817524315</v>
+        <v>0.997945522737853</v>
       </c>
       <c r="R4" t="n">
         <v>0.999026524050469</v>
@@ -1669,7 +1669,7 @@
         <v>2.89323191492191</v>
       </c>
       <c r="U4" t="n">
-        <v>1.1261297916822</v>
+        <v>1.10641430554187</v>
       </c>
       <c r="V4" t="n">
         <v>0.999769549580697</v>
@@ -1687,16 +1687,16 @@
         <v>149</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.3359293631417</v>
+        <v>2.29503355936848</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.000633902133824072</v>
+        <v>0.00062280422235237</v>
       </c>
       <c r="AC4" t="n">
         <v>1.10869208822785</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0314898091802709</v>
+        <v>0.0309385078107122</v>
       </c>
       <c r="AE4" t="s">
         <v>98</v>
@@ -1705,7 +1705,7 @@
         <v>111</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0272394087536914</v>
+        <v>0.0267625203970198</v>
       </c>
       <c r="AH4" t="n">
         <v>0.665073921237439</v>
@@ -1717,7 +1717,7 @@
         <v>1.76089172033418</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0314898091802709</v>
+        <v>0.0309385078107122</v>
       </c>
       <c r="AL4" t="n">
         <v>0.665931303103025</v>
@@ -1735,10 +1735,10 @@
         <v>149</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.3359293631417</v>
+        <v>2.29503355936848</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.0044373149367685</v>
+        <v>0.00435962955646659</v>
       </c>
       <c r="AS4" t="n">
         <v>1.15603864478166</v>
@@ -1771,46 +1771,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.00110334045492523</v>
+        <v>0.00108402394841966</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.00283716116980773</v>
+        <v>0.00278749015307913</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.00846341714439373</v>
+        <v>0.00831524560622593</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0113704905825324</v>
+        <v>0.0111714240529508</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.00643986492672325</v>
+        <v>0.00632712031358345</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.00865187456234416</v>
+        <v>0.00850040364462075</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.00540450501404703</v>
+        <v>0.00530988675202536</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.00726088201928903</v>
+        <v>0.00713376361795091</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0223967656902464</v>
+        <v>0.0220046589128432</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0332717862500995</v>
+        <v>0.0326892872828197</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0169603554319344</v>
+        <v>0.0166634254910668</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0251956612156184</v>
+        <v>0.0247545533494008</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0142059286319262</v>
+        <v>0.0139572212527929</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0211037891569967</v>
+        <v>0.0207343189008092</v>
       </c>
       <c r="BQ4" t="b">
         <v>0</v>
@@ -1873,10 +1873,10 @@
         <v>0.999769549580697</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.00424977845517345</v>
+        <v>0.00417537633132298</v>
       </c>
       <c r="CL4" t="n">
-        <v>7.40975312299795</v>
+        <v>7.40975312299796</v>
       </c>
     </row>
     <row r="5">
@@ -1918,7 +1918,7 @@
         <v>300</v>
       </c>
       <c r="N5" t="n">
-        <v>1.20842158337</v>
+        <v>1.1872653905807</v>
       </c>
       <c r="O5" t="s">
         <v>98</v>
@@ -1927,7 +1927,7 @@
         <v>99</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.12550151487279</v>
+        <v>1.10579702815972</v>
       </c>
       <c r="R5" t="n">
         <v>0.997341812842276</v>
@@ -1939,7 +1939,7 @@
         <v>2.44875624758245</v>
       </c>
       <c r="U5" t="n">
-        <v>1.20842158337</v>
+        <v>1.1872653905807</v>
       </c>
       <c r="V5" t="n">
         <v>0.997707251307285</v>
@@ -1957,16 +1957,16 @@
         <v>69</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.33232743441018</v>
+        <v>2.29149469066478</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.0013760043860827</v>
+        <v>0.00135191427177863</v>
       </c>
       <c r="AC5" t="n">
         <v>1.07367388439862</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0384520122066485</v>
+        <v>0.0377788214969031</v>
       </c>
       <c r="AE5" t="s">
         <v>98</v>
@@ -1975,7 +1975,7 @@
         <v>111</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0384203355769582</v>
+        <v>0.0377476994393041</v>
       </c>
       <c r="AH5" t="n">
         <v>0.497133148131768</v>
@@ -1987,7 +1987,7 @@
         <v>1.61652391538232</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0384520122066485</v>
+        <v>0.0377788214969031</v>
       </c>
       <c r="AL5" t="n">
         <v>0.496975719496566</v>
@@ -2005,10 +2005,10 @@
         <v>69</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.33232743441018</v>
+        <v>2.29149469066478</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.00963203070257893</v>
+        <v>0.00946339990245041</v>
       </c>
       <c r="AS5" t="n">
         <v>1.00082447561206</v>
@@ -2041,46 +2041,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.00237992595347978</v>
+        <v>0.00233825988843345</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.00611980959466228</v>
+        <v>0.00601266828454316</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0182557487375312</v>
+        <v>0.0179361399643022</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0245263603997917</v>
+        <v>0.0240969701802039</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0138909088374281</v>
+        <v>0.0136477166026753</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0186622549053272</v>
+        <v>0.0183355293088188</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.011657618182335</v>
+        <v>0.0114535248252454</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0156618580291535</v>
+        <v>0.0153876612649916</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0586395090878207</v>
+        <v>0.0576128899207977</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.0688436469069749</v>
+        <v>0.06763838089193</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0441475863616049</v>
+        <v>0.0433746815566081</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0518299162894042</v>
+        <v>0.0509225146703318</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0368908629780899</v>
+        <v>0.0362450037679692</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0433104162102322</v>
+        <v>0.0425521679897948</v>
       </c>
       <c r="BQ5" t="b">
         <v>0</v>
@@ -2143,10 +2143,10 @@
         <v>0.997707251307285</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.00865559441587176</v>
+        <v>0.0085040583735764</v>
       </c>
       <c r="CL5" t="n">
-        <v>4.44244616362096</v>
+        <v>4.44244616362095</v>
       </c>
     </row>
     <row r="6">
@@ -2190,7 +2190,7 @@
         <v>600</v>
       </c>
       <c r="N6" t="n">
-        <v>1.32386833098952</v>
+        <v>1.30069097796678</v>
       </c>
       <c r="O6" t="s">
         <v>98</v>
@@ -2199,7 +2199,7 @@
         <v>111</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.30314854895781</v>
+        <v>1.28033394326534</v>
       </c>
       <c r="R6" t="n">
         <v>0.999791962695814</v>
@@ -2211,7 +2211,7 @@
         <v>0.710998752972665</v>
       </c>
       <c r="U6" t="n">
-        <v>1.32386833098952</v>
+        <v>1.30069097796678</v>
       </c>
       <c r="V6" t="n">
         <v>0.999795764899988</v>
@@ -2229,16 +2229,16 @@
         <v>62</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.33394904079873</v>
+        <v>2.29308790711238</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00153549278999916</v>
+        <v>0.00150861046520551</v>
       </c>
       <c r="AC6" t="n">
         <v>1.01589978521503</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.353678991732009</v>
+        <v>0.347487029392391</v>
       </c>
       <c r="AE6" t="s">
         <v>98</v>
@@ -2247,7 +2247,7 @@
         <v>111</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.330400946519775</v>
+        <v>0.324616519777869</v>
       </c>
       <c r="AH6" t="n">
         <v>0.99007467292149</v>
@@ -2259,7 +2259,7 @@
         <v>1.25113422504825</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.353678991732009</v>
+        <v>0.347487029392391</v>
       </c>
       <c r="AL6" t="n">
         <v>0.990407805013714</v>
@@ -2277,10 +2277,10 @@
         <v>62</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.33394904079873</v>
+        <v>2.29308790711238</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0107484495299941</v>
+        <v>0.0105602732564386</v>
       </c>
       <c r="AS6" t="n">
         <v>1.07045393016403</v>
@@ -2313,46 +2313,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.00265221481908947</v>
+        <v>0.0026057817126277</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.00681998096337291</v>
+        <v>0.00670058154675696</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0203444007425777</v>
+        <v>0.0199882253231579</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0273324371355108</v>
+        <v>0.0268539201035427</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0154801766901109</v>
+        <v>0.0152091606746942</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.020797415543607</v>
+        <v>0.0204333090605592</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0129913738086131</v>
+        <v>0.0127639299987082</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0174537413227757</v>
+        <v>0.0171481735297133</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0294459990566072</v>
+        <v>0.0289304792732068</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0751429825423309</v>
+        <v>0.0738274322018649</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0221407899614785</v>
+        <v>0.0217531646265964</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0565008845633134</v>
+        <v>0.0555117069261065</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0184919891478902</v>
+        <v>0.0181682444441756</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.0471895422886355</v>
+        <v>0.046363381064741</v>
       </c>
       <c r="BQ6" t="b">
         <v>0</v>
@@ -2415,10 +2415,10 @@
         <v>0.999795764899988</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.00941541203539683</v>
+        <v>0.0092505736421135</v>
       </c>
       <c r="CL6" t="n">
-        <v>37.5638358047814</v>
+        <v>37.5638358047815</v>
       </c>
     </row>
     <row r="7">
@@ -2456,7 +2456,7 @@
         <v>600</v>
       </c>
       <c r="N7" t="n">
-        <v>1.34106207568664</v>
+        <v>1.31758370670838</v>
       </c>
       <c r="O7" t="s">
         <v>98</v>
@@ -2465,7 +2465,7 @@
         <v>99</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.31933987276378</v>
+        <v>1.29624180079376</v>
       </c>
       <c r="R7" t="n">
         <v>0.999887278397298</v>
@@ -2477,7 +2477,7 @@
         <v>1.003946291558</v>
       </c>
       <c r="U7" t="n">
-        <v>1.34106207568664</v>
+        <v>1.31758370670838</v>
       </c>
       <c r="V7" t="n">
         <v>0.999894443336438</v>
@@ -2495,16 +2495,16 @@
         <v>117</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.3331479824422</v>
+        <v>2.29230087312057</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.000807317640983459</v>
+        <v>0.000793183693121306</v>
       </c>
       <c r="AC7" t="n">
         <v>1.0164644481466</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.396629714787707</v>
+        <v>0.389685801481711</v>
       </c>
       <c r="AE7" t="s">
         <v>98</v>
@@ -2513,7 +2513,7 @@
         <v>99</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.369704402424142</v>
+        <v>0.36323187849675</v>
       </c>
       <c r="AH7" t="n">
         <v>0.997780915269485</v>
@@ -2525,7 +2525,7 @@
         <v>1.24952730832149</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.396629714787707</v>
+        <v>0.389685801481711</v>
       </c>
       <c r="AL7" t="n">
         <v>0.998122550225431</v>
@@ -2543,10 +2543,10 @@
         <v>117</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.3331479824422</v>
+        <v>2.29230087312057</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.00565122348688421</v>
+        <v>0.00555228585184914</v>
       </c>
       <c r="AS7" t="n">
         <v>1.07282929872356</v>
@@ -2579,46 +2579,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.00140309586572985</v>
+        <v>0.00137853145290756</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.00360796079759103</v>
+        <v>0.00354479516461944</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0107627573630939</v>
+        <v>0.0105743305980877</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0144596241862196</v>
+        <v>0.0142064752842516</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.00818944670632634</v>
+        <v>0.00804607164935854</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.011002414871175</v>
+        <v>0.0108097923515462</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0068728003289243</v>
+        <v>0.00675247618810943</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.00923351763033742</v>
+        <v>0.00907186371600885</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.022068301006293</v>
+        <v>0.0216819447569123</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0348591134871735</v>
+        <v>0.0342488247141591</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0166890994985485</v>
+        <v>0.0163969185152475</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0263621206386815</v>
+        <v>0.0259005912235816</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.013971101001381</v>
+        <v>0.0137265048187808</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0220687671066761</v>
+        <v>0.0216824026971385</v>
       </c>
       <c r="BQ7" t="b">
         <v>0</v>
@@ -2681,10 +2681,10 @@
         <v>0.999894443336438</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.00443625812396188</v>
+        <v>0.00435859124559322</v>
       </c>
       <c r="CL7" t="n">
-        <v>89.4063653882902</v>
+        <v>89.4063653882905</v>
       </c>
     </row>
     <row r="8">
@@ -2726,7 +2726,7 @@
         <v>600</v>
       </c>
       <c r="N8" t="n">
-        <v>1.09834555739463</v>
+        <v>1.07911649803215</v>
       </c>
       <c r="O8" t="s">
         <v>98</v>
@@ -2735,7 +2735,7 @@
         <v>99</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.932800122520638</v>
+        <v>0.916469315873757</v>
       </c>
       <c r="R8" t="n">
         <v>0.998014485619764</v>
@@ -2747,7 +2747,7 @@
         <v>4.23502656211206</v>
       </c>
       <c r="U8" t="n">
-        <v>1.09834555739463</v>
+        <v>1.07911649803215</v>
       </c>
       <c r="V8" t="n">
         <v>0.999860422432155</v>
@@ -2765,16 +2765,16 @@
         <v>166</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.33411295450244</v>
+        <v>2.29324895113058</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.000567910694526141</v>
+        <v>0.00055796811463031</v>
       </c>
       <c r="AC8" t="n">
         <v>1.17747149778095</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0337112943119567</v>
+        <v>0.0331211007475123</v>
       </c>
       <c r="AE8" t="s">
         <v>98</v>
@@ -2783,7 +2783,7 @@
         <v>111</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0336412225079778</v>
+        <v>0.0330522557112562</v>
       </c>
       <c r="AH8" t="n">
         <v>0.859726359528916</v>
@@ -2795,7 +2795,7 @@
         <v>1.38250632850401</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0337112943119567</v>
+        <v>0.0331211007475123</v>
       </c>
       <c r="AL8" t="n">
         <v>0.859492457974167</v>
@@ -2813,10 +2813,10 @@
         <v>166</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.33411295450244</v>
+        <v>2.29324895113058</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.00397537486168299</v>
+        <v>0.00390577680241217</v>
       </c>
       <c r="AS8" t="n">
         <v>1.00208291491079</v>
@@ -2849,46 +2849,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.000989030912924763</v>
+        <v>0.00097171565725872</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.00254322234752082</v>
+        <v>0.00249869740437957</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.00758658050415642</v>
+        <v>0.00745376000345841</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0101924719890802</v>
+        <v>0.0100140293781835</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.00577267466189381</v>
+        <v>0.00567161074534545</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.00775551314076094</v>
+        <v>0.00761973508660841</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.00484458129318898</v>
+        <v>0.00475976578076134</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.00650863180092774</v>
+        <v>0.00639468326585523</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0122566145578361</v>
+        <v>0.0120420343946727</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.0287891862976474</v>
+        <v>0.028285165528785</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.00928619101882867</v>
+        <v>0.00912361493596466</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0218120494835727</v>
+        <v>0.0214301795051192</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.0077796550849569</v>
+        <v>0.00764345437067255</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0182733934003882</v>
+        <v>0.0179534757168466</v>
       </c>
       <c r="BQ8" t="b">
         <v>0</v>
@@ -2951,10 +2951,10 @@
         <v>0.999860422432155</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.00368222630795402</v>
+        <v>0.00361776048680602</v>
       </c>
       <c r="CL8" t="n">
-        <v>9.15513917195598</v>
+        <v>9.15513917195597</v>
       </c>
     </row>
     <row r="9">
@@ -2996,7 +2996,7 @@
         <v>900</v>
       </c>
       <c r="N9" t="n">
-        <v>1.25398474563604</v>
+        <v>1.2320308651372</v>
       </c>
       <c r="O9" t="s">
         <v>98</v>
@@ -3005,7 +3005,7 @@
         <v>99</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.10063846684457</v>
+        <v>1.08136926484062</v>
       </c>
       <c r="R9" t="n">
         <v>0.998731607593589</v>
@@ -3017,7 +3017,7 @@
         <v>4.6166245421767</v>
       </c>
       <c r="U9" t="n">
-        <v>1.25398474563604</v>
+        <v>1.2320308651372</v>
       </c>
       <c r="V9" t="n">
         <v>0.9999173464781</v>
@@ -3035,16 +3035,16 @@
         <v>192</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.33605629372157</v>
+        <v>2.29515826773728</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.000491801324994015</v>
+        <v>0.00048319121426048</v>
       </c>
       <c r="AC9" t="n">
         <v>1.13932484045474</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0765684447151247</v>
+        <v>0.0752279383883071</v>
       </c>
       <c r="AE9" t="s">
         <v>98</v>
@@ -3053,7 +3053,7 @@
         <v>111</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0760943600684935</v>
+        <v>0.0747621536813002</v>
       </c>
       <c r="AH9" t="n">
         <v>0.970695174412968</v>
@@ -3065,7 +3065,7 @@
         <v>1.55605584008292</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0765684447151247</v>
+        <v>0.0752279383883071</v>
       </c>
       <c r="AL9" t="n">
         <v>0.97052787072339</v>
@@ -3083,10 +3083,10 @@
         <v>192</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.33605629372157</v>
+        <v>2.29515826773728</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.0034426092749581</v>
+        <v>0.00338233849982336</v>
       </c>
       <c r="AS9" t="n">
         <v>1.00623022056043</v>
@@ -3119,46 +3119,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.000857043713629507</v>
+        <v>0.00084203919675896</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.00220382669219016</v>
+        <v>0.00216524364880875</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.00657414348132317</v>
+        <v>0.00645904801395527</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.00883227604964717</v>
+        <v>0.00867764678992012</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0050023052516871</v>
+        <v>0.0049147284194358</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.00672053188267315</v>
+        <v>0.00660287355042126</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.0041980669039114</v>
+        <v>0.00412457010942858</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.00564004814856435</v>
+        <v>0.00554130616347068</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0114415465821301</v>
+        <v>0.0112412360542228</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0220719967509512</v>
+        <v>0.0216855757990796</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.00867378406030165</v>
+        <v>0.00852192956654063</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0167326796445895</v>
+        <v>0.0164397356908284</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.00726834228332826</v>
+        <v>0.00714109327294902</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0140214284940276</v>
+        <v>0.0137759512131817</v>
       </c>
       <c r="BQ9" t="b">
         <v>0</v>
@@ -3221,7 +3221,7 @@
         <v>0.9999173464781</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.00282761986998374</v>
+        <v>0.00277811589560303</v>
       </c>
       <c r="CL9" t="n">
         <v>27.0787617274612</v>
@@ -3260,7 +3260,7 @@
         <v>300</v>
       </c>
       <c r="N10" t="n">
-        <v>1.34102040741186</v>
+        <v>1.31754276793237</v>
       </c>
       <c r="O10" t="s">
         <v>98</v>
@@ -3269,7 +3269,7 @@
         <v>99</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.26070021803685</v>
+        <v>1.2386287677836</v>
       </c>
       <c r="R10" t="n">
         <v>0.999713524615498</v>
@@ -3281,7 +3281,7 @@
         <v>1.7955954188882</v>
       </c>
       <c r="U10" t="n">
-        <v>1.34102040741186</v>
+        <v>1.31754276793237</v>
       </c>
       <c r="V10" t="n">
         <v>0.999884540341955</v>
@@ -3299,16 +3299,16 @@
         <v>70</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.32526764396137</v>
+        <v>2.28455849804792</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.000814454516273686</v>
+        <v>0.000800195621032545</v>
       </c>
       <c r="AC10" t="n">
         <v>1.06371077614318</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.00965562852738834</v>
+        <v>0.00948658459318646</v>
       </c>
       <c r="AE10" t="s">
         <v>98</v>
@@ -3317,7 +3317,7 @@
         <v>111</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.00966301603762399</v>
+        <v>0.00949384276810327</v>
       </c>
       <c r="AH10" t="n">
         <v>0.030518900730106</v>
@@ -3329,7 +3329,7 @@
         <v>3.79189154513842</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.00965562852738834</v>
+        <v>0.00948658459318646</v>
       </c>
       <c r="AL10" t="n">
         <v>0.0305018423219471</v>
@@ -3347,10 +3347,10 @@
         <v>70</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.32526764396137</v>
+        <v>2.28455849804792</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.0057011816139158</v>
+        <v>0.00560136934722782</v>
       </c>
       <c r="AS10" t="n">
         <v>0.999235486083549</v>
@@ -3383,46 +3383,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.00141538030501996</v>
+        <v>0.00139060082489873</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.00363954935576562</v>
+        <v>0.00357583069259674</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0108569878733894</v>
+        <v>0.0106669113870692</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0145862216481693</v>
+        <v>0.014330856367126</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.0082611472674503</v>
+        <v>0.00811651692762834</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0110987436401713</v>
+        <v>0.0109044346643951</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.00693297333666805</v>
+        <v>0.00681159572927329</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.00931435928167043</v>
+        <v>0.00915129004872749</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.318962894540822</v>
+        <v>0.313378717145777</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0776704733515835</v>
+        <v>0.0763106734846531</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.24017397000184</v>
+        <v>0.235969173528277</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0584846270712045</v>
+        <v>0.0574607194692911</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.200708439322574</v>
+        <v>0.197194577525347</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0488743981029014</v>
+        <v>0.0480187396117294</v>
       </c>
       <c r="BQ10" t="b">
         <v>0</v>
@@ -3485,10 +3485,10 @@
         <v>0.999884540341955</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.00976957114357704</v>
+        <v>0.00959853238241397</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.98833698895129</v>
+        <v>0.988336988951288</v>
       </c>
     </row>
   </sheetData>

--- a/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled_with_mdf.xlsx
+++ b/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled_with_mdf.xlsx
@@ -323,10 +323,10 @@
     <t xml:space="preserve">AICc | MDF</t>
   </si>
   <si>
-    <t xml:space="preserve">MDF (LM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">MDF (HM)</t>
+    <t xml:space="preserve">Noise (LM.MAE) | MDF (LM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Noise (HM.MAE) | MDF (HM)</t>
   </si>
   <si>
     <t xml:space="preserve">YMF_1.25m</t>
@@ -1108,7 +1108,7 @@
         <v>300</v>
       </c>
       <c r="N2" t="n">
-        <v>1.12174549713261</v>
+        <v>1.10147085029077</v>
       </c>
       <c r="O2" t="s">
         <v>98</v>
@@ -1117,7 +1117,7 @@
         <v>99</v>
       </c>
       <c r="Q2" t="n">
-        <v>1.07119650180274</v>
+        <v>1.05183548735893</v>
       </c>
       <c r="R2" t="n">
         <v>0.998592889197321</v>
@@ -1129,7 +1129,7 @@
         <v>1.1975836661462</v>
       </c>
       <c r="U2" t="n">
-        <v>1.12174549713261</v>
+        <v>1.10147085029077</v>
       </c>
       <c r="V2" t="n">
         <v>0.998747896186046</v>
@@ -1147,16 +1147,16 @@
         <v>48</v>
       </c>
       <c r="AA2" t="n">
-        <v>2.28895217995805</v>
+        <v>2.24758121193978</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00194804440847494</v>
+        <v>0.00334746137948478</v>
       </c>
       <c r="AC2" t="n">
         <v>1.04718928342727</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.00476396815325628</v>
+        <v>-0.00514805392791875</v>
       </c>
       <c r="AE2" t="s">
         <v>98</v>
@@ -1165,7 +1165,7 @@
         <v>102</v>
       </c>
       <c r="AG2" t="n">
-        <v>-0.00396562808995602</v>
+        <v>-0.00389395255460912</v>
       </c>
       <c r="AH2" t="n">
         <v>-0.016477614613488</v>
@@ -1177,13 +1177,13 @@
         <v>1.65939118535001</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.00476396815325628</v>
+        <v>-0.00514805392791875</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.0160211732658191</v>
+        <v>-0.0157938412604248</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.6590185751789</v>
+        <v>1.65883296432331</v>
       </c>
       <c r="AN2" t="s">
         <v>103</v>
@@ -1195,13 +1195,13 @@
         <v>48</v>
       </c>
       <c r="AQ2" t="n">
-        <v>2.28895217995805</v>
+        <v>2.24758121193978</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.0136363108593246</v>
+        <v>0.00860775783296085</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.20131491032209</v>
+        <v>1.32206385561252</v>
       </c>
       <c r="AT2" t="n">
         <v>0.68126764428177</v>
@@ -1231,46 +1231,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC2" t="n">
-        <v>0.00335202202085907</v>
+        <v>0.00329143692125072</v>
       </c>
       <c r="BD2" t="n">
-        <v>0.00861948519649475</v>
+        <v>0.008463694940359</v>
       </c>
       <c r="BE2" t="n">
-        <v>0.0257124267610096</v>
+        <v>0.0252476953461221</v>
       </c>
       <c r="BF2" t="n">
-        <v>0.0345443100998252</v>
+        <v>0.0339199495033626</v>
       </c>
       <c r="BG2" t="n">
-        <v>0.019564739921729</v>
+        <v>0.0192111229974985</v>
       </c>
       <c r="BH2" t="n">
-        <v>0.0262849729883723</v>
+        <v>0.0258098932613319</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0164192473302872</v>
+        <v>0.0161224826524869</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.022059044704534</v>
+        <v>0.0216603452293</v>
       </c>
       <c r="BK2" t="n">
-        <v>0.0525953904924861</v>
+        <v>0.0516447711492664</v>
       </c>
       <c r="BL2" t="n">
-        <v>0.128724340348185</v>
+        <v>0.126397751521058</v>
       </c>
       <c r="BM2" t="n">
-        <v>0.0394002599359597</v>
+        <v>0.0386881319553078</v>
       </c>
       <c r="BN2" t="n">
-        <v>0.096429980314111</v>
+        <v>0.0946870860472458</v>
       </c>
       <c r="BO2" t="n">
-        <v>0.0328579667389861</v>
+        <v>0.0322640854412436</v>
       </c>
       <c r="BP2" t="n">
-        <v>0.0804180756916869</v>
+        <v>0.0789645837110931</v>
       </c>
       <c r="BQ2" t="b">
         <v>0</v>
@@ -1327,16 +1327,16 @@
         <v>1</v>
       </c>
       <c r="CI2" t="n">
-        <v>-0.0160211732658191</v>
+        <v>-0.0157938412604248</v>
       </c>
       <c r="CJ2" t="n">
         <v>0.998747896186046</v>
       </c>
       <c r="CK2" t="n">
-        <v>0.0159687004078233</v>
+        <v>0.0156800790029508</v>
       </c>
       <c r="CL2" t="n">
-        <v>0.298331613192665</v>
+        <v>0.328318111595608</v>
       </c>
     </row>
     <row r="3">
@@ -1378,7 +1378,7 @@
         <v>300</v>
       </c>
       <c r="N3" t="n">
-        <v>1.30748519423355</v>
+        <v>1.28385345188934</v>
       </c>
       <c r="O3" t="s">
         <v>98</v>
@@ -1387,7 +1387,7 @@
         <v>99</v>
       </c>
       <c r="Q3" t="n">
-        <v>1.2500716114784</v>
+        <v>1.22747757342384</v>
       </c>
       <c r="R3" t="n">
         <v>0.999633472356177</v>
@@ -1399,7 +1399,7 @@
         <v>1.1474396140762</v>
       </c>
       <c r="U3" t="n">
-        <v>1.30748519423355</v>
+        <v>1.28385345188934</v>
       </c>
       <c r="V3" t="n">
         <v>0.99977497116895</v>
@@ -1417,16 +1417,16 @@
         <v>77</v>
       </c>
       <c r="AA3" t="n">
-        <v>2.2892168995484</v>
+        <v>2.24784114693663</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00120803002614691</v>
+        <v>0.00207584274783066</v>
       </c>
       <c r="AC3" t="n">
         <v>1.04592823501308</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.0452083702163778</v>
+        <v>0.0443912653180071</v>
       </c>
       <c r="AE3" t="s">
         <v>98</v>
@@ -1435,7 +1435,7 @@
         <v>111</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.0380952811319747</v>
+        <v>0.037406739592681</v>
       </c>
       <c r="AH3" t="n">
         <v>0.693680686527493</v>
@@ -1447,7 +1447,7 @@
         <v>1.20999491759047</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.0452083702163778</v>
+        <v>0.0443912653180071</v>
       </c>
       <c r="AL3" t="n">
         <v>0.695258815852541</v>
@@ -1456,19 +1456,19 @@
         <v>1.20687400068568</v>
       </c>
       <c r="AN3" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AO3" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AP3" t="n">
         <v>77</v>
       </c>
       <c r="AQ3" t="n">
-        <v>2.2892168995484</v>
+        <v>2.24784114693663</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.00845621018302839</v>
+        <v>0.00533788135156456</v>
       </c>
       <c r="AS3" t="n">
         <v>1.18671837752715</v>
@@ -1501,46 +1501,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.00209197366799462</v>
+        <v>0.00205416292800998</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.0053793608605576</v>
+        <v>0.00528213324345422</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.0160469470037929</v>
+        <v>0.0157569113546877</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.0215588640701574</v>
+        <v>0.0211692049572382</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.0122102183347026</v>
+        <v>0.0119895284676778</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.0164042691287369</v>
+        <v>0.016107775169872</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0102471382495419</v>
+        <v>0.0100619294747529</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0137668966301046</v>
+        <v>0.0135180710560355</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.0293959272254283</v>
+        <v>0.0288646195049092</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.0540862909158513</v>
+        <v>0.0531087247476721</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.0221566648218679</v>
+        <v>0.0217562009415984</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.0407665936199463</v>
+        <v>0.0400297702578717</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.0185232829091659</v>
+        <v>0.0181884894820517</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.0340814447001055</v>
+        <v>0.0334654500231304</v>
       </c>
       <c r="BQ3" t="b">
         <v>0</v>
@@ -1603,10 +1603,10 @@
         <v>0.99977497116895</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.00682136933223095</v>
+        <v>0.00669807857283652</v>
       </c>
       <c r="CL3" t="n">
-        <v>6.62746261264118</v>
+        <v>6.62746261264119</v>
       </c>
     </row>
     <row r="4">
@@ -1648,7 +1648,7 @@
         <v>600</v>
       </c>
       <c r="N4" t="n">
-        <v>1.10641430554187</v>
+        <v>1.09731407372464</v>
       </c>
       <c r="O4" t="s">
         <v>98</v>
@@ -1657,7 +1657,7 @@
         <v>99</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.997945522737853</v>
+        <v>0.989737444125356</v>
       </c>
       <c r="R4" t="n">
         <v>0.999026524050469</v>
@@ -1669,7 +1669,7 @@
         <v>2.89323191492191</v>
       </c>
       <c r="U4" t="n">
-        <v>1.10641430554187</v>
+        <v>1.09731407372464</v>
       </c>
       <c r="V4" t="n">
         <v>0.999769549580697</v>
@@ -1687,16 +1687,16 @@
         <v>149</v>
       </c>
       <c r="AA4" t="n">
-        <v>2.29503355936848</v>
+        <v>2.2761569619547</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00062280422235237</v>
+        <v>0.00108094292630142</v>
       </c>
       <c r="AC4" t="n">
         <v>1.10869208822785</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.0309385078107122</v>
+        <v>0.0306840393066931</v>
       </c>
       <c r="AE4" t="s">
         <v>98</v>
@@ -1705,7 +1705,7 @@
         <v>111</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.0267625203970198</v>
+        <v>0.0265423992919272</v>
       </c>
       <c r="AH4" t="n">
         <v>0.665073921237439</v>
@@ -1717,7 +1717,7 @@
         <v>1.76089172033418</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.0309385078107122</v>
+        <v>0.0306840393066931</v>
       </c>
       <c r="AL4" t="n">
         <v>0.665931303103025</v>
@@ -1726,19 +1726,19 @@
         <v>1.75863641061905</v>
       </c>
       <c r="AN4" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AO4" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AP4" t="n">
         <v>149</v>
       </c>
       <c r="AQ4" t="n">
-        <v>2.29503355936848</v>
+        <v>2.2761569619547</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.00435962955646659</v>
+        <v>0.00277956752477507</v>
       </c>
       <c r="AS4" t="n">
         <v>1.15603864478166</v>
@@ -1771,46 +1771,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.00108402394841966</v>
+        <v>0.00107510787676673</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.00278749015307913</v>
+        <v>0.00276456311168587</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.00831524560622593</v>
+        <v>0.00824685290535902</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.0111714240529508</v>
+        <v>0.0110795393510799</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.00632712031358345</v>
+        <v>0.00627507989680587</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.00850040364462075</v>
+        <v>0.00843048802321333</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.00530988675202536</v>
+        <v>0.005266213057529</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.00713376361795091</v>
+        <v>0.00707508857883812</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.0220046589128432</v>
+        <v>0.0218236711073143</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.0326892872828197</v>
+        <v>0.0324204186585408</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.0166634254910668</v>
+        <v>0.0165263692056607</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.0247545533494008</v>
+        <v>0.0245509477263688</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.0139572212527929</v>
+        <v>0.0138424234340296</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.0207343189008092</v>
+        <v>0.0205637796122041</v>
       </c>
       <c r="BQ4" t="b">
         <v>0</v>
@@ -1873,10 +1873,10 @@
         <v>0.999769549580697</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.00417537633132298</v>
+        <v>0.00414103395853471</v>
       </c>
       <c r="CL4" t="n">
-        <v>7.40975312299796</v>
+        <v>7.40975312299794</v>
       </c>
     </row>
     <row r="5">
@@ -1918,7 +1918,7 @@
         <v>300</v>
       </c>
       <c r="N5" t="n">
-        <v>1.1872653905807</v>
+        <v>1.16702933478796</v>
       </c>
       <c r="O5" t="s">
         <v>98</v>
@@ -1927,7 +1927,7 @@
         <v>99</v>
       </c>
       <c r="Q5" t="n">
-        <v>1.10579702815972</v>
+        <v>1.08694954002875</v>
       </c>
       <c r="R5" t="n">
         <v>0.997341812842276</v>
@@ -1939,7 +1939,7 @@
         <v>2.44875624758245</v>
       </c>
       <c r="U5" t="n">
-        <v>1.1872653905807</v>
+        <v>1.16702933478796</v>
       </c>
       <c r="V5" t="n">
         <v>0.997707251307285</v>
@@ -1957,16 +1957,16 @@
         <v>69</v>
       </c>
       <c r="AA5" t="n">
-        <v>2.29149469066478</v>
+        <v>2.25243786750044</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00135191427177863</v>
+        <v>0.00232552582190311</v>
       </c>
       <c r="AC5" t="n">
         <v>1.07367388439862</v>
       </c>
       <c r="AD5" t="n">
-        <v>0.0377788214969031</v>
+        <v>0.0371349095748844</v>
       </c>
       <c r="AE5" t="s">
         <v>98</v>
@@ -1975,7 +1975,7 @@
         <v>111</v>
       </c>
       <c r="AG5" t="n">
-        <v>0.0377476994393041</v>
+        <v>0.0371043179696165</v>
       </c>
       <c r="AH5" t="n">
         <v>0.497133148131768</v>
@@ -1987,7 +1987,7 @@
         <v>1.61652391538232</v>
       </c>
       <c r="AK5" t="n">
-        <v>0.0377788214969031</v>
+        <v>0.0371349095748844</v>
       </c>
       <c r="AL5" t="n">
         <v>0.496975719496566</v>
@@ -1996,19 +1996,19 @@
         <v>1.61678069534197</v>
       </c>
       <c r="AN5" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AO5" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AP5" t="n">
         <v>69</v>
       </c>
       <c r="AQ5" t="n">
-        <v>2.29149469066478</v>
+        <v>2.25243786750044</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.00946339990245041</v>
+        <v>0.00597992354203657</v>
       </c>
       <c r="AS5" t="n">
         <v>1.00082447561206</v>
@@ -2041,46 +2041,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC5" t="n">
-        <v>0.00233825988843345</v>
+        <v>0.00229840598724535</v>
       </c>
       <c r="BD5" t="n">
-        <v>0.00601266828454316</v>
+        <v>0.00591018682434518</v>
       </c>
       <c r="BE5" t="n">
-        <v>0.0179361399643022</v>
+        <v>0.0176304317950054</v>
       </c>
       <c r="BF5" t="n">
-        <v>0.0240969701802039</v>
+        <v>0.0236862552407547</v>
       </c>
       <c r="BG5" t="n">
-        <v>0.0136477166026753</v>
+        <v>0.0134151014209255</v>
       </c>
       <c r="BH5" t="n">
-        <v>0.0183355293088188</v>
+        <v>0.0180230138451101</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0114535248252454</v>
+        <v>0.0112583080108533</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0153876612649916</v>
+        <v>0.0151253900202063</v>
       </c>
       <c r="BK5" t="n">
-        <v>0.0576128899207977</v>
+        <v>0.0566309210500907</v>
       </c>
       <c r="BL5" t="n">
-        <v>0.06763838089193</v>
+        <v>0.0664855349820615</v>
       </c>
       <c r="BM5" t="n">
-        <v>0.0433746815566081</v>
+        <v>0.0426353923606665</v>
       </c>
       <c r="BN5" t="n">
-        <v>0.0509225146703318</v>
+        <v>0.0500545782711488</v>
       </c>
       <c r="BO5" t="n">
-        <v>0.0362450037679692</v>
+        <v>0.0356272346286718</v>
       </c>
       <c r="BP5" t="n">
-        <v>0.0425521679897948</v>
+        <v>0.0418268979260206</v>
       </c>
       <c r="BQ5" t="b">
         <v>0</v>
@@ -2143,10 +2143,10 @@
         <v>0.997707251307285</v>
       </c>
       <c r="CK5" t="n">
-        <v>0.0085040583735764</v>
+        <v>0.00835911302178087</v>
       </c>
       <c r="CL5" t="n">
-        <v>4.44244616362095</v>
+        <v>4.44244616362096</v>
       </c>
     </row>
     <row r="6">
@@ -2190,7 +2190,7 @@
         <v>600</v>
       </c>
       <c r="N6" t="n">
-        <v>1.30069097796678</v>
+        <v>1.28564109992505</v>
       </c>
       <c r="O6" t="s">
         <v>98</v>
@@ -2199,7 +2199,7 @@
         <v>111</v>
       </c>
       <c r="Q6" t="n">
-        <v>1.28033394326534</v>
+        <v>1.26551960994157</v>
       </c>
       <c r="R6" t="n">
         <v>0.999791962695814</v>
@@ -2211,7 +2211,7 @@
         <v>0.710998752972665</v>
       </c>
       <c r="U6" t="n">
-        <v>1.30069097796678</v>
+        <v>1.28564109992505</v>
       </c>
       <c r="V6" t="n">
         <v>0.999795764899988</v>
@@ -2229,16 +2229,16 @@
         <v>62</v>
       </c>
       <c r="AA6" t="n">
-        <v>2.29308790711238</v>
+        <v>2.26655532256648</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.00150861046520551</v>
+        <v>0.0026095209305864</v>
       </c>
       <c r="AC6" t="n">
         <v>1.01589978521503</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.347487029392391</v>
+        <v>0.343466368449842</v>
       </c>
       <c r="AE6" t="s">
         <v>98</v>
@@ -2247,7 +2247,7 @@
         <v>111</v>
       </c>
       <c r="AG6" t="n">
-        <v>0.324616519777869</v>
+        <v>0.320860486165164</v>
       </c>
       <c r="AH6" t="n">
         <v>0.99007467292149</v>
@@ -2259,7 +2259,7 @@
         <v>1.25113422504825</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.347487029392391</v>
+        <v>0.343466368449842</v>
       </c>
       <c r="AL6" t="n">
         <v>0.990407805013714</v>
@@ -2268,19 +2268,19 @@
         <v>1.22995859003021</v>
       </c>
       <c r="AN6" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AO6" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AP6" t="n">
         <v>62</v>
       </c>
       <c r="AQ6" t="n">
-        <v>2.29308790711238</v>
+        <v>2.26655532256648</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0105602732564386</v>
+        <v>0.00671019667865075</v>
       </c>
       <c r="AS6" t="n">
         <v>1.07045393016403</v>
@@ -2313,46 +2313,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0026057817126277</v>
+        <v>0.002575631048371</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.00670058154675696</v>
+        <v>0.00662305126723971</v>
       </c>
       <c r="BE6" t="n">
-        <v>0.0199882253231579</v>
+        <v>0.0197569479802072</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0268539201035427</v>
+        <v>0.0265432020088171</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.0152091606746942</v>
+        <v>0.0150331803556572</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0204333090605592</v>
+        <v>0.0201968817964669</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0127639299987082</v>
+        <v>0.012616242659388</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0171481735297133</v>
+        <v>0.0169497575149702</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0289304792732068</v>
+        <v>0.0285957339784935</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0738274322018649</v>
+        <v>0.0729731986678485</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.0217531646265964</v>
+        <v>0.0215014657371619</v>
       </c>
       <c r="BN6" t="n">
-        <v>0.0555117069261065</v>
+        <v>0.0548693987735338</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0181682444441756</v>
+        <v>0.017958025516122</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.046363381064741</v>
+        <v>0.0458269252559085</v>
       </c>
       <c r="BQ6" t="b">
         <v>0</v>
@@ -2415,10 +2415,10 @@
         <v>0.999795764899988</v>
       </c>
       <c r="CK6" t="n">
-        <v>0.0092505736421135</v>
+        <v>0.00914353822210358</v>
       </c>
       <c r="CL6" t="n">
-        <v>37.5638358047815</v>
+        <v>37.5638358047814</v>
       </c>
     </row>
     <row r="7">
@@ -2456,7 +2456,7 @@
         <v>600</v>
       </c>
       <c r="N7" t="n">
-        <v>1.31758370670838</v>
+        <v>1.29958847440573</v>
       </c>
       <c r="O7" t="s">
         <v>98</v>
@@ -2465,7 +2465,7 @@
         <v>99</v>
       </c>
       <c r="Q7" t="n">
-        <v>1.29624180079376</v>
+        <v>1.27853805096221</v>
       </c>
       <c r="R7" t="n">
         <v>0.999887278397298</v>
@@ -2477,7 +2477,7 @@
         <v>1.003946291558</v>
       </c>
       <c r="U7" t="n">
-        <v>1.31758370670838</v>
+        <v>1.29958847440573</v>
       </c>
       <c r="V7" t="n">
         <v>0.999894443336438</v>
@@ -2495,16 +2495,16 @@
         <v>117</v>
       </c>
       <c r="AA7" t="n">
-        <v>2.29230087312057</v>
+        <v>2.26099319489918</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.000793183693121306</v>
+        <v>0.00136911352632303</v>
       </c>
       <c r="AC7" t="n">
         <v>1.0164644481466</v>
       </c>
       <c r="AD7" t="n">
-        <v>0.389685801481711</v>
+        <v>0.384363569211378</v>
       </c>
       <c r="AE7" t="s">
         <v>98</v>
@@ -2513,7 +2513,7 @@
         <v>99</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.36323187849675</v>
+        <v>0.358270947361978</v>
       </c>
       <c r="AH7" t="n">
         <v>0.997780915269485</v>
@@ -2525,7 +2525,7 @@
         <v>1.24952730832149</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.389685801481711</v>
+        <v>0.384363569211378</v>
       </c>
       <c r="AL7" t="n">
         <v>0.998122550225431</v>
@@ -2534,7 +2534,7 @@
         <v>1.14932531698564</v>
       </c>
       <c r="AN7" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AO7" t="s">
         <v>99</v>
@@ -2543,10 +2543,10 @@
         <v>117</v>
       </c>
       <c r="AQ7" t="n">
-        <v>2.29230087312057</v>
+        <v>2.26099319489918</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.00555228585184914</v>
+        <v>0.00352057763911637</v>
       </c>
       <c r="AS7" t="n">
         <v>1.07282929872356</v>
@@ -2579,46 +2579,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC7" t="n">
-        <v>0.00137853145290756</v>
+        <v>0.00135970381136549</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.00354479516461944</v>
+        <v>0.00349638122922554</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0105743305980877</v>
+        <v>0.0104299090068151</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0142064752842516</v>
+        <v>0.0140124467594297</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.00804607164935854</v>
+        <v>0.0079361803933292</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0108097923515462</v>
+        <v>0.010662154881897</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.00675247618810943</v>
+        <v>0.00666025253886083</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.00907186371600885</v>
+        <v>0.00894796244570899</v>
       </c>
       <c r="BK7" t="n">
-        <v>0.0216819447569123</v>
+        <v>0.0213858181194263</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0342488247141591</v>
+        <v>0.0337810627391999</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0163969185152475</v>
+        <v>0.0161729734586813</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.0259005912235816</v>
+        <v>0.0255468473563257</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0137265048187808</v>
+        <v>0.013539031611834</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0216824026971385</v>
+        <v>0.0213862698052182</v>
       </c>
       <c r="BQ7" t="b">
         <v>0</v>
@@ -2681,10 +2681,10 @@
         <v>0.999894443336438</v>
       </c>
       <c r="CK7" t="n">
-        <v>0.00435859124559322</v>
+        <v>0.00429906268465443</v>
       </c>
       <c r="CL7" t="n">
-        <v>89.4063653882905</v>
+        <v>89.4063653882903</v>
       </c>
     </row>
     <row r="8">
@@ -2726,7 +2726,7 @@
         <v>600</v>
       </c>
       <c r="N8" t="n">
-        <v>1.07911649803215</v>
+        <v>1.06700748829</v>
       </c>
       <c r="O8" t="s">
         <v>98</v>
@@ -2735,7 +2735,7 @@
         <v>99</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.916469315873757</v>
+        <v>0.906185406866212</v>
       </c>
       <c r="R8" t="n">
         <v>0.998014485619764</v>
@@ -2747,7 +2747,7 @@
         <v>4.23502656211206</v>
       </c>
       <c r="U8" t="n">
-        <v>1.07911649803215</v>
+        <v>1.06700748829</v>
       </c>
       <c r="V8" t="n">
         <v>0.999860422432155</v>
@@ -2765,16 +2765,16 @@
         <v>166</v>
       </c>
       <c r="AA8" t="n">
-        <v>2.29324895113058</v>
+        <v>2.26751588714622</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.00055796811463031</v>
+        <v>0.000965487299879778</v>
       </c>
       <c r="AC8" t="n">
         <v>1.17747149778095</v>
       </c>
       <c r="AD8" t="n">
-        <v>0.0331211007475123</v>
+        <v>0.0327494414017846</v>
       </c>
       <c r="AE8" t="s">
         <v>98</v>
@@ -2783,7 +2783,7 @@
         <v>111</v>
       </c>
       <c r="AG8" t="n">
-        <v>0.0330522557112562</v>
+        <v>0.0326813688912162</v>
       </c>
       <c r="AH8" t="n">
         <v>0.859726359528916</v>
@@ -2795,7 +2795,7 @@
         <v>1.38250632850401</v>
       </c>
       <c r="AK8" t="n">
-        <v>0.0331211007475123</v>
+        <v>0.0327494414017846</v>
       </c>
       <c r="AL8" t="n">
         <v>0.859492457974167</v>
@@ -2804,19 +2804,19 @@
         <v>1.38367415839523</v>
       </c>
       <c r="AN8" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AO8" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AP8" t="n">
         <v>166</v>
       </c>
       <c r="AQ8" t="n">
-        <v>2.29324895113058</v>
+        <v>2.26751588714622</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.00390577680241217</v>
+        <v>0.00248268162826229</v>
       </c>
       <c r="AS8" t="n">
         <v>1.00208291491079</v>
@@ -2849,46 +2849,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC8" t="n">
-        <v>0.00097171565725872</v>
+        <v>0.000960811816587381</v>
       </c>
       <c r="BD8" t="n">
-        <v>0.00249869740437957</v>
+        <v>0.00247065895693898</v>
       </c>
       <c r="BE8" t="n">
-        <v>0.00745376000345841</v>
+        <v>0.00737011968041433</v>
       </c>
       <c r="BF8" t="n">
-        <v>0.0100140293781835</v>
+        <v>0.009901659694725</v>
       </c>
       <c r="BG8" t="n">
-        <v>0.00567161074534545</v>
+        <v>0.00560796832129358</v>
       </c>
       <c r="BH8" t="n">
-        <v>0.00761973508660841</v>
+        <v>0.0075342323197017</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.00475976578076134</v>
+        <v>0.00470635537482765</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.00639468326585523</v>
+        <v>0.00632292708187929</v>
       </c>
       <c r="BK8" t="n">
-        <v>0.0120420343946727</v>
+        <v>0.0119069080092765</v>
       </c>
       <c r="BL8" t="n">
-        <v>0.028285165528785</v>
+        <v>0.027967771303443</v>
       </c>
       <c r="BM8" t="n">
-        <v>0.00912361493596466</v>
+        <v>0.00902123679389679</v>
       </c>
       <c r="BN8" t="n">
-        <v>0.0214301795051192</v>
+        <v>0.0211897066248723</v>
       </c>
       <c r="BO8" t="n">
-        <v>0.00764345437067255</v>
+        <v>0.00755768544432677</v>
       </c>
       <c r="BP8" t="n">
-        <v>0.0179534757168466</v>
+        <v>0.0177520157143748</v>
       </c>
       <c r="BQ8" t="b">
         <v>0</v>
@@ -2951,10 +2951,10 @@
         <v>0.999860422432155</v>
       </c>
       <c r="CK8" t="n">
-        <v>0.00361776048680602</v>
+        <v>0.00357716477998528</v>
       </c>
       <c r="CL8" t="n">
-        <v>9.15513917195597</v>
+        <v>9.155139171956</v>
       </c>
     </row>
     <row r="9">
@@ -2996,7 +2996,7 @@
         <v>900</v>
       </c>
       <c r="N9" t="n">
-        <v>1.2320308651372</v>
+        <v>1.2190721160156</v>
       </c>
       <c r="O9" t="s">
         <v>98</v>
@@ -3005,7 +3005,7 @@
         <v>99</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.08136926484062</v>
+        <v>1.06999520481712</v>
       </c>
       <c r="R9" t="n">
         <v>0.998731607593589</v>
@@ -3017,7 +3017,7 @@
         <v>4.6166245421767</v>
       </c>
       <c r="U9" t="n">
-        <v>1.2320308651372</v>
+        <v>1.2190721160156</v>
       </c>
       <c r="V9" t="n">
         <v>0.9999173464781</v>
@@ -3035,16 +3035,16 @@
         <v>192</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.29515826773728</v>
+        <v>2.27101733017835</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.00048319121426048</v>
+        <v>0.000836690595328864</v>
       </c>
       <c r="AC9" t="n">
         <v>1.13932484045474</v>
       </c>
       <c r="AD9" t="n">
-        <v>0.0752279383883071</v>
+        <v>0.0744366757599961</v>
       </c>
       <c r="AE9" t="s">
         <v>98</v>
@@ -3053,7 +3053,7 @@
         <v>111</v>
       </c>
       <c r="AG9" t="n">
-        <v>0.0747621536813002</v>
+        <v>0.0739757902704793</v>
       </c>
       <c r="AH9" t="n">
         <v>0.970695174412968</v>
@@ -3065,7 +3065,7 @@
         <v>1.55605584008292</v>
       </c>
       <c r="AK9" t="n">
-        <v>0.0752279383883071</v>
+        <v>0.0744366757599961</v>
       </c>
       <c r="AL9" t="n">
         <v>0.97052787072339</v>
@@ -3074,19 +3074,19 @@
         <v>1.56049523863239</v>
       </c>
       <c r="AN9" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="AO9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="AP9" t="n">
         <v>192</v>
       </c>
       <c r="AQ9" t="n">
-        <v>2.29515826773728</v>
+        <v>2.27101733017835</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.00338233849982336</v>
+        <v>0.00215149010227422</v>
       </c>
       <c r="AS9" t="n">
         <v>1.00623022056043</v>
@@ -3119,46 +3119,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC9" t="n">
-        <v>0.00084203919675896</v>
+        <v>0.00083318245866082</v>
       </c>
       <c r="BD9" t="n">
-        <v>0.00216524364880875</v>
+        <v>0.00214246917941354</v>
       </c>
       <c r="BE9" t="n">
-        <v>0.00645904801395527</v>
+        <v>0.00639111044425175</v>
       </c>
       <c r="BF9" t="n">
-        <v>0.00867764678992012</v>
+        <v>0.00858637355083302</v>
       </c>
       <c r="BG9" t="n">
-        <v>0.0049147284194358</v>
+        <v>0.00486303431469344</v>
       </c>
       <c r="BH9" t="n">
-        <v>0.00660287355042126</v>
+        <v>0.00653342319471774</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.00412457010942858</v>
+        <v>0.00408118704915391</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.00554130616347068</v>
+        <v>0.00548302158764526</v>
       </c>
       <c r="BK9" t="n">
-        <v>0.0112412360542228</v>
+        <v>0.0111229984662164</v>
       </c>
       <c r="BL9" t="n">
-        <v>0.0216855757990796</v>
+        <v>0.0214574825391707</v>
       </c>
       <c r="BM9" t="n">
-        <v>0.00852192956654063</v>
+        <v>0.00843229419261486</v>
       </c>
       <c r="BN9" t="n">
-        <v>0.0164397356908284</v>
+        <v>0.0162668192351851</v>
       </c>
       <c r="BO9" t="n">
-        <v>0.00714109327294902</v>
+        <v>0.00706598181365313</v>
       </c>
       <c r="BP9" t="n">
-        <v>0.0137759512131817</v>
+        <v>0.0136310529799195</v>
       </c>
       <c r="BQ9" t="b">
         <v>0</v>
@@ -3221,7 +3221,7 @@
         <v>0.9999173464781</v>
       </c>
       <c r="CK9" t="n">
-        <v>0.00277811589560303</v>
+        <v>0.00274889511230893</v>
       </c>
       <c r="CL9" t="n">
         <v>27.0787617274612</v>
@@ -3260,7 +3260,7 @@
         <v>300</v>
       </c>
       <c r="N10" t="n">
-        <v>1.31754276793237</v>
+        <v>1.29592767022994</v>
       </c>
       <c r="O10" t="s">
         <v>98</v>
@@ -3269,7 +3269,7 @@
         <v>99</v>
       </c>
       <c r="Q10" t="n">
-        <v>1.2386287677836</v>
+        <v>1.21830830268424</v>
       </c>
       <c r="R10" t="n">
         <v>0.999713524615498</v>
@@ -3281,7 +3281,7 @@
         <v>1.7955954188882</v>
       </c>
       <c r="U10" t="n">
-        <v>1.31754276793237</v>
+        <v>1.29592767022994</v>
       </c>
       <c r="V10" t="n">
         <v>0.999884540341955</v>
@@ -3299,16 +3299,16 @@
         <v>70</v>
       </c>
       <c r="AA10" t="n">
-        <v>2.28455849804792</v>
+        <v>2.24707891382181</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.000800195621032545</v>
+        <v>0.00137736886136188</v>
       </c>
       <c r="AC10" t="n">
         <v>1.06371077614318</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.00948658459318646</v>
+        <v>0.00933095135088507</v>
       </c>
       <c r="AE10" t="s">
         <v>98</v>
@@ -3317,7 +3317,7 @@
         <v>111</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.00949384276810327</v>
+        <v>0.00933809045098793</v>
       </c>
       <c r="AH10" t="n">
         <v>0.030518900730106</v>
@@ -3329,7 +3329,7 @@
         <v>3.79189154513842</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.00948658459318646</v>
+        <v>0.00933095135088507</v>
       </c>
       <c r="AL10" t="n">
         <v>0.0305018423219471</v>
@@ -3347,10 +3347,10 @@
         <v>70</v>
       </c>
       <c r="AQ10" t="n">
-        <v>2.28455849804792</v>
+        <v>2.24707891382181</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.00560136934722782</v>
+        <v>0.00354180564350198</v>
       </c>
       <c r="AS10" t="n">
         <v>0.999235486083549</v>
@@ -3383,46 +3383,46 @@
         <v>1.40029850566019</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.00139060082489873</v>
+        <v>0.00136778716493501</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.00357583069259674</v>
+        <v>0.00351716699554718</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0106669113870692</v>
+        <v>0.010491914159331</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.014330856367126</v>
+        <v>0.0140957498733754</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.00811651692762834</v>
+        <v>0.00798336048621017</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.0109044346643951</v>
+        <v>0.010725540721521</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.00681159572927329</v>
+        <v>0.0066998473209626</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.00915129004872749</v>
+        <v>0.0090011575192029</v>
       </c>
       <c r="BK10" t="n">
-        <v>0.313378717145777</v>
+        <v>0.308237546966081</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0763106734846531</v>
+        <v>0.0750587500532054</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.235969173528277</v>
+        <v>0.23209795441895</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0574607194692911</v>
+        <v>0.0565180411019468</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.197194577525347</v>
+        <v>0.193959479459962</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.0480187396117294</v>
+        <v>0.0472309627186241</v>
       </c>
       <c r="BQ10" t="b">
         <v>0</v>
@@ -3485,10 +3485,10 @@
         <v>0.999884540341955</v>
       </c>
       <c r="CK10" t="n">
-        <v>0.00959853238241397</v>
+        <v>0.00944106256792635</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.988336988951288</v>
+        <v>0.988336988951291</v>
       </c>
     </row>
   </sheetData>

--- a/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled_with_mdf.xlsx
+++ b/data processing/goFlux_reprocessing/ymf_black_oak/results/ymf_black_oak_flux_compiled_with_mdf.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="153" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="157">
   <si>
     <t xml:space="preserve">instrument</t>
   </si>
@@ -176,6 +176,15 @@
     <t xml:space="preserve">mad_sd_CH4</t>
   </si>
   <si>
+    <t xml:space="preserve">field_day</t>
+  </si>
+  <si>
+    <t xml:space="preserve">empirical_sd_CH4</t>
+  </si>
+  <si>
+    <t xml:space="preserve">empirical_sd_CO2</t>
+  </si>
+  <si>
     <t xml:space="preserve">CO2_MDF_goflux</t>
   </si>
   <si>
@@ -314,58 +323,61 @@
     <t xml:space="preserve"/>
   </si>
   <si>
+    <t xml:space="preserve">AICc | MDF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDF (LM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">MDF (HM)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-04</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YMF_1.25m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-04 13:00:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-04 13:05:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-04 12:38:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-04 12:43:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AICc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">YMF_10m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-04 10:26:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-04 10:36:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-04 10:04:00</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2022-10-04 10:14:00</t>
+  </si>
+  <si>
     <t xml:space="preserve">Noise (LM.MAE)</t>
   </si>
   <si>
     <t xml:space="preserve">Noise (HM.MAE)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AICc | MDF</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noise (LM.MAE) | MDF (LM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Noise (HM.MAE) | MDF (HM)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YMF_1.25m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1.25</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-10-04 13:00:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-10-04 13:05:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-10-04 12:38:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-10-04 12:43:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AICc</t>
-  </si>
-  <si>
-    <t xml:space="preserve">YMF_10m</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10.0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-10-04 10:26:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-10-04 10:36:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-10-04 10:04:00</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2022-10-04 10:14:00</t>
   </si>
   <si>
     <t xml:space="preserve">YMF_2m</t>
@@ -1070,19 +1082,28 @@
       <c r="CL1" t="s">
         <v>89</v>
       </c>
+      <c r="CM1" t="s">
+        <v>90</v>
+      </c>
+      <c r="CN1" t="s">
+        <v>91</v>
+      </c>
+      <c r="CO1" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B2" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="C2" t="s">
-        <v>92</v>
+        <v>95</v>
       </c>
       <c r="D2" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E2" t="n">
         <v>12.9</v>
@@ -1093,16 +1114,16 @@
       </c>
       <c r="H2"/>
       <c r="I2" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="J2" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="K2" t="s">
-        <v>96</v>
+        <v>99</v>
       </c>
       <c r="L2" t="s">
-        <v>97</v>
+        <v>100</v>
       </c>
       <c r="M2" t="n">
         <v>300</v>
@@ -1111,10 +1132,10 @@
         <v>1.10147085029077</v>
       </c>
       <c r="O2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P2" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q2" t="n">
         <v>1.05183548735893</v>
@@ -1138,10 +1159,10 @@
         <v>1.12969676375376</v>
       </c>
       <c r="X2" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Y2" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z2" t="n">
         <v>48</v>
@@ -1150,19 +1171,19 @@
         <v>2.24758121193978</v>
       </c>
       <c r="AB2" t="n">
-        <v>0.00334746137948478</v>
+        <v>0.0103194294544325</v>
       </c>
       <c r="AC2" t="n">
         <v>1.04718928342727</v>
       </c>
       <c r="AD2" t="n">
-        <v>-0.00514805392791875</v>
+        <v>-0.00437387748466349</v>
       </c>
       <c r="AE2" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AF2" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="AG2" t="n">
         <v>-0.00389395255460912</v>
@@ -1177,19 +1198,19 @@
         <v>1.65939118535001</v>
       </c>
       <c r="AK2" t="n">
-        <v>-0.00514805392791875</v>
+        <v>-0.00437387748466349</v>
       </c>
       <c r="AL2" t="n">
-        <v>-0.0157938412604248</v>
+        <v>-0.0161857955795053</v>
       </c>
       <c r="AM2" t="n">
-        <v>1.65883296432331</v>
+        <v>1.65915297218831</v>
       </c>
       <c r="AN2" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="AO2" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="AP2" t="n">
         <v>48</v>
@@ -1198,10 +1219,10 @@
         <v>2.24758121193978</v>
       </c>
       <c r="AR2" t="n">
-        <v>0.00860775783296085</v>
+        <v>0.0210851045068941</v>
       </c>
       <c r="AS2" t="n">
-        <v>1.32206385561252</v>
+        <v>1.12324878727305</v>
       </c>
       <c r="AT2" t="n">
         <v>0.68126764428177</v>
@@ -1230,57 +1251,57 @@
       <c r="BB2" t="n">
         <v>1.40029850566019</v>
       </c>
-      <c r="BC2" t="n">
+      <c r="BC2" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD2" t="n">
+        <v>1.14395825018492</v>
+      </c>
+      <c r="BE2" t="n">
+        <v>0.559873746783635</v>
+      </c>
+      <c r="BF2" t="n">
         <v>0.00329143692125072</v>
       </c>
-      <c r="BD2" t="n">
+      <c r="BG2" t="n">
         <v>0.008463694940359</v>
       </c>
-      <c r="BE2" t="n">
-        <v>0.0252476953461221</v>
-      </c>
-      <c r="BF2" t="n">
-        <v>0.0339199495033626</v>
-      </c>
-      <c r="BG2" t="n">
-        <v>0.0192111229974985</v>
-      </c>
       <c r="BH2" t="n">
-        <v>0.0258098932613319</v>
+        <v>0.0135620291976287</v>
       </c>
       <c r="BI2" t="n">
-        <v>0.0161224826524869</v>
+        <v>0.0277105245227218</v>
       </c>
       <c r="BJ2" t="n">
-        <v>0.0216603452293</v>
+        <v>0.0103194294544325</v>
       </c>
       <c r="BK2" t="n">
+        <v>0.0210851045068941</v>
+      </c>
+      <c r="BL2" t="n">
+        <v>0.00866033820013098</v>
+      </c>
+      <c r="BM2" t="n">
+        <v>0.0176951775116186</v>
+      </c>
+      <c r="BN2" t="n">
         <v>0.0516447711492664</v>
       </c>
-      <c r="BL2" t="n">
+      <c r="BO2" t="n">
         <v>0.126397751521058</v>
       </c>
-      <c r="BM2" t="n">
+      <c r="BP2" t="n">
         <v>0.0386881319553078</v>
       </c>
-      <c r="BN2" t="n">
+      <c r="BQ2" t="n">
         <v>0.0946870860472458</v>
       </c>
-      <c r="BO2" t="n">
+      <c r="BR2" t="n">
         <v>0.0322640854412436</v>
       </c>
-      <c r="BP2" t="n">
+      <c r="BS2" t="n">
         <v>0.0789645837110931</v>
       </c>
-      <c r="BQ2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BR2" t="b">
-        <v>0</v>
-      </c>
-      <c r="BS2" t="b">
-        <v>0</v>
-      </c>
       <c r="BT2" t="b">
         <v>0</v>
       </c>
@@ -1300,13 +1321,13 @@
         <v>0</v>
       </c>
       <c r="BZ2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CA2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB2" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC2" t="b">
         <v>1</v>
@@ -1326,31 +1347,40 @@
       <c r="CH2" t="b">
         <v>1</v>
       </c>
-      <c r="CI2" t="n">
-        <v>-0.0157938412604248</v>
-      </c>
-      <c r="CJ2" t="n">
+      <c r="CI2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CJ2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CK2" t="b">
+        <v>1</v>
+      </c>
+      <c r="CL2" t="n">
+        <v>-0.0161857955795053</v>
+      </c>
+      <c r="CM2" t="n">
         <v>0.998747896186046</v>
       </c>
-      <c r="CK2" t="n">
+      <c r="CN2" t="n">
         <v>0.0156800790029508</v>
       </c>
-      <c r="CL2" t="n">
-        <v>0.328318111595608</v>
+      <c r="CO2" t="n">
+        <v>0.278944862703841</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B3" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C3" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="D3" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E3" t="n">
         <v>12.9</v>
@@ -1363,16 +1393,16 @@
       </c>
       <c r="H3"/>
       <c r="I3" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="J3" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="K3" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="L3" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="M3" t="n">
         <v>300</v>
@@ -1381,10 +1411,10 @@
         <v>1.28385345188934</v>
       </c>
       <c r="O3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P3" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q3" t="n">
         <v>1.22747757342384</v>
@@ -1408,10 +1438,10 @@
         <v>0.899074238592826</v>
       </c>
       <c r="X3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Y3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z3" t="n">
         <v>77</v>
@@ -1420,7 +1450,7 @@
         <v>2.24784114693663</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.00207584274783066</v>
+        <v>0.006440284268141</v>
       </c>
       <c r="AC3" t="n">
         <v>1.04592823501308</v>
@@ -1429,10 +1459,10 @@
         <v>0.0443912653180071</v>
       </c>
       <c r="AE3" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AF3" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG3" t="n">
         <v>0.037406739592681</v>
@@ -1456,10 +1486,10 @@
         <v>1.20687400068568</v>
       </c>
       <c r="AN3" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AO3" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AP3" t="n">
         <v>77</v>
@@ -1468,7 +1498,7 @@
         <v>2.24784114693663</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.00533788135156456</v>
+        <v>0.0131590673154446</v>
       </c>
       <c r="AS3" t="n">
         <v>1.18671837752715</v>
@@ -1500,57 +1530,57 @@
       <c r="BB3" t="n">
         <v>1.40029850566019</v>
       </c>
-      <c r="BC3" t="n">
+      <c r="BC3" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD3" t="n">
+        <v>1.14395825018492</v>
+      </c>
+      <c r="BE3" t="n">
+        <v>0.559873746783635</v>
+      </c>
+      <c r="BF3" t="n">
         <v>0.00205416292800998</v>
       </c>
-      <c r="BD3" t="n">
+      <c r="BG3" t="n">
         <v>0.00528213324345422</v>
       </c>
-      <c r="BE3" t="n">
-        <v>0.0157569113546877</v>
-      </c>
-      <c r="BF3" t="n">
-        <v>0.0211692049572382</v>
-      </c>
-      <c r="BG3" t="n">
-        <v>0.0119895284676778</v>
-      </c>
       <c r="BH3" t="n">
-        <v>0.016107775169872</v>
+        <v>0.00846396825243476</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.0100619294747529</v>
+        <v>0.0172939459428123</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.0135180710560355</v>
+        <v>0.00644028426814099</v>
       </c>
       <c r="BK3" t="n">
+        <v>0.0131590673154446</v>
+      </c>
+      <c r="BL3" t="n">
+        <v>0.00540485693645853</v>
+      </c>
+      <c r="BM3" t="n">
+        <v>0.011043437416115</v>
+      </c>
+      <c r="BN3" t="n">
         <v>0.0288646195049092</v>
       </c>
-      <c r="BL3" t="n">
+      <c r="BO3" t="n">
         <v>0.0531087247476721</v>
       </c>
-      <c r="BM3" t="n">
+      <c r="BP3" t="n">
         <v>0.0217562009415984</v>
       </c>
-      <c r="BN3" t="n">
+      <c r="BQ3" t="n">
         <v>0.0400297702578717</v>
       </c>
-      <c r="BO3" t="n">
+      <c r="BR3" t="n">
         <v>0.0181884894820517</v>
       </c>
-      <c r="BP3" t="n">
+      <c r="BS3" t="n">
         <v>0.0334654500231304</v>
       </c>
-      <c r="BQ3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BR3" t="b">
-        <v>0</v>
-      </c>
-      <c r="BS3" t="b">
-        <v>0</v>
-      </c>
       <c r="BT3" t="b">
         <v>0</v>
       </c>
@@ -1582,7 +1612,7 @@
         <v>0</v>
       </c>
       <c r="CD3" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE3" t="b">
         <v>0</v>
@@ -1596,31 +1626,40 @@
       <c r="CH3" t="b">
         <v>0</v>
       </c>
-      <c r="CI3" t="n">
+      <c r="CI3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ3" t="b">
+        <v>1</v>
+      </c>
+      <c r="CK3" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL3" t="n">
         <v>0.695258815852541</v>
       </c>
-      <c r="CJ3" t="n">
+      <c r="CM3" t="n">
         <v>0.99977497116895</v>
       </c>
-      <c r="CK3" t="n">
+      <c r="CN3" t="n">
         <v>0.00669807857283652</v>
       </c>
-      <c r="CL3" t="n">
+      <c r="CO3" t="n">
         <v>6.62746261264119</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B4" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="D4" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E4" t="n">
         <v>10.6</v>
@@ -1633,16 +1672,16 @@
       </c>
       <c r="H4"/>
       <c r="I4" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="J4" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="K4" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="L4" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="M4" t="n">
         <v>600</v>
@@ -1651,10 +1690,10 @@
         <v>1.09731407372464</v>
       </c>
       <c r="O4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P4" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q4" t="n">
         <v>0.989737444125356</v>
@@ -1678,10 +1717,10 @@
         <v>1.40769764878489</v>
       </c>
       <c r="X4" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Y4" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="Z4" t="n">
         <v>149</v>
@@ -1690,7 +1729,7 @@
         <v>2.2761569619547</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.00108094292630142</v>
+        <v>0.00337071624206704</v>
       </c>
       <c r="AC4" t="n">
         <v>1.10869208822785</v>
@@ -1699,10 +1738,10 @@
         <v>0.0306840393066931</v>
       </c>
       <c r="AE4" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AF4" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG4" t="n">
         <v>0.0265423992919272</v>
@@ -1726,10 +1765,10 @@
         <v>1.75863641061905</v>
       </c>
       <c r="AN4" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AO4" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AP4" t="n">
         <v>149</v>
@@ -1738,7 +1777,7 @@
         <v>2.2761569619547</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.00277956752477507</v>
+        <v>0.00688719318649359</v>
       </c>
       <c r="AS4" t="n">
         <v>1.15603864478166</v>
@@ -1770,57 +1809,57 @@
       <c r="BB4" t="n">
         <v>1.40029850566019</v>
       </c>
-      <c r="BC4" t="n">
+      <c r="BC4" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD4" t="n">
+        <v>1.14395825018492</v>
+      </c>
+      <c r="BE4" t="n">
+        <v>0.559873746783635</v>
+      </c>
+      <c r="BF4" t="n">
         <v>0.00107510787676673</v>
       </c>
-      <c r="BD4" t="n">
+      <c r="BG4" t="n">
         <v>0.00276456311168587</v>
       </c>
-      <c r="BE4" t="n">
-        <v>0.00824685290535902</v>
-      </c>
-      <c r="BF4" t="n">
-        <v>0.0110795393510799</v>
-      </c>
-      <c r="BG4" t="n">
-        <v>0.00627507989680587</v>
-      </c>
       <c r="BH4" t="n">
-        <v>0.00843048802321333</v>
+        <v>0.00442987204803256</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.005266213057529</v>
+        <v>0.00905130613057446</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.00707508857883812</v>
+        <v>0.00337071624206704</v>
       </c>
       <c r="BK4" t="n">
+        <v>0.0068871931864936</v>
+      </c>
+      <c r="BL4" t="n">
+        <v>0.00282879424311937</v>
+      </c>
+      <c r="BM4" t="n">
+        <v>0.00577991472377892</v>
+      </c>
+      <c r="BN4" t="n">
         <v>0.0218236711073143</v>
       </c>
-      <c r="BL4" t="n">
+      <c r="BO4" t="n">
         <v>0.0324204186585408</v>
       </c>
-      <c r="BM4" t="n">
+      <c r="BP4" t="n">
         <v>0.0165263692056607</v>
       </c>
-      <c r="BN4" t="n">
+      <c r="BQ4" t="n">
         <v>0.0245509477263688</v>
       </c>
-      <c r="BO4" t="n">
+      <c r="BR4" t="n">
         <v>0.0138424234340296</v>
       </c>
-      <c r="BP4" t="n">
+      <c r="BS4" t="n">
         <v>0.0205637796122041</v>
       </c>
-      <c r="BQ4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BR4" t="b">
-        <v>0</v>
-      </c>
-      <c r="BS4" t="b">
-        <v>0</v>
-      </c>
       <c r="BT4" t="b">
         <v>0</v>
       </c>
@@ -1852,7 +1891,7 @@
         <v>0</v>
       </c>
       <c r="CD4" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE4" t="b">
         <v>0</v>
@@ -1866,31 +1905,40 @@
       <c r="CH4" t="b">
         <v>0</v>
       </c>
-      <c r="CI4" t="n">
+      <c r="CI4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ4" t="b">
+        <v>1</v>
+      </c>
+      <c r="CK4" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL4" t="n">
         <v>0.665931303103025</v>
       </c>
-      <c r="CJ4" t="n">
+      <c r="CM4" t="n">
         <v>0.999769549580697</v>
       </c>
-      <c r="CK4" t="n">
+      <c r="CN4" t="n">
         <v>0.00414103395853471</v>
       </c>
-      <c r="CL4" t="n">
+      <c r="CO4" t="n">
         <v>7.40975312299794</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="C5" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
       <c r="D5" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E5" t="n">
         <v>12.9</v>
@@ -1903,16 +1951,16 @@
       </c>
       <c r="H5"/>
       <c r="I5" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="J5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="K5" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="L5" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="M5" t="n">
         <v>300</v>
@@ -1921,10 +1969,10 @@
         <v>1.16702933478796</v>
       </c>
       <c r="O5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P5" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q5" t="n">
         <v>1.08694954002875</v>
@@ -1948,10 +1996,10 @@
         <v>2.27421231286376</v>
       </c>
       <c r="X5" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Y5" t="s">
-        <v>101</v>
+        <v>121</v>
       </c>
       <c r="Z5" t="n">
         <v>69</v>
@@ -1960,7 +2008,7 @@
         <v>2.25243786750044</v>
       </c>
       <c r="AB5" t="n">
-        <v>0.00232552582190311</v>
+        <v>0.00720604374639235</v>
       </c>
       <c r="AC5" t="n">
         <v>1.07367388439862</v>
@@ -1969,10 +2017,10 @@
         <v>0.0371349095748844</v>
       </c>
       <c r="AE5" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AF5" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG5" t="n">
         <v>0.0371043179696165</v>
@@ -1996,10 +2044,10 @@
         <v>1.61678069534197</v>
       </c>
       <c r="AN5" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AO5" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AP5" t="n">
         <v>69</v>
@@ -2008,7 +2056,7 @@
         <v>2.25243786750044</v>
       </c>
       <c r="AR5" t="n">
-        <v>0.00597992354203657</v>
+        <v>0.0147237001953311</v>
       </c>
       <c r="AS5" t="n">
         <v>1.00082447561206</v>
@@ -2040,57 +2088,57 @@
       <c r="BB5" t="n">
         <v>1.40029850566019</v>
       </c>
-      <c r="BC5" t="n">
+      <c r="BC5" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD5" t="n">
+        <v>1.14395825018492</v>
+      </c>
+      <c r="BE5" t="n">
+        <v>0.559873746783635</v>
+      </c>
+      <c r="BF5" t="n">
         <v>0.00229840598724535</v>
       </c>
-      <c r="BD5" t="n">
+      <c r="BG5" t="n">
         <v>0.00591018682434518</v>
       </c>
-      <c r="BE5" t="n">
-        <v>0.0176304317950054</v>
-      </c>
-      <c r="BF5" t="n">
-        <v>0.0236862552407547</v>
-      </c>
-      <c r="BG5" t="n">
-        <v>0.0134151014209255</v>
-      </c>
       <c r="BH5" t="n">
-        <v>0.0180230138451101</v>
+        <v>0.0094703467977084</v>
       </c>
       <c r="BI5" t="n">
-        <v>0.0112583080108533</v>
+        <v>0.0193502221055876</v>
       </c>
       <c r="BJ5" t="n">
-        <v>0.0151253900202063</v>
+        <v>0.00720604374639234</v>
       </c>
       <c r="BK5" t="n">
+        <v>0.0147237001953311</v>
+      </c>
+      <c r="BL5" t="n">
+        <v>0.00604750254888277</v>
+      </c>
+      <c r="BM5" t="n">
+        <v>0.0123565187215008</v>
+      </c>
+      <c r="BN5" t="n">
         <v>0.0566309210500907</v>
       </c>
-      <c r="BL5" t="n">
+      <c r="BO5" t="n">
         <v>0.0664855349820615</v>
       </c>
-      <c r="BM5" t="n">
+      <c r="BP5" t="n">
         <v>0.0426353923606665</v>
       </c>
-      <c r="BN5" t="n">
+      <c r="BQ5" t="n">
         <v>0.0500545782711488</v>
       </c>
-      <c r="BO5" t="n">
+      <c r="BR5" t="n">
         <v>0.0356272346286718</v>
       </c>
-      <c r="BP5" t="n">
+      <c r="BS5" t="n">
         <v>0.0418268979260206</v>
       </c>
-      <c r="BQ5" t="b">
-        <v>0</v>
-      </c>
-      <c r="BR5" t="b">
-        <v>0</v>
-      </c>
-      <c r="BS5" t="b">
-        <v>0</v>
-      </c>
       <c r="BT5" t="b">
         <v>0</v>
       </c>
@@ -2122,45 +2170,54 @@
         <v>0</v>
       </c>
       <c r="CD5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF5" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG5" t="b">
         <v>1</v>
       </c>
       <c r="CH5" t="b">
-        <v>0</v>
-      </c>
-      <c r="CI5" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI5" t="b">
+        <v>1</v>
+      </c>
+      <c r="CJ5" t="b">
+        <v>1</v>
+      </c>
+      <c r="CK5" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL5" t="n">
         <v>0.496975719496566</v>
       </c>
-      <c r="CJ5" t="n">
+      <c r="CM5" t="n">
         <v>0.997707251307285</v>
       </c>
-      <c r="CK5" t="n">
+      <c r="CN5" t="n">
         <v>0.00835911302178087</v>
       </c>
-      <c r="CL5" t="n">
+      <c r="CO5" t="n">
         <v>4.44244616362096</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B6" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="C6" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="D6" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E6" t="n">
         <v>11.5</v>
@@ -2172,19 +2229,19 @@
         <v>9.4</v>
       </c>
       <c r="H6" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="I6" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="J6" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="K6" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="L6" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="M6" t="n">
         <v>600</v>
@@ -2193,10 +2250,10 @@
         <v>1.28564109992505</v>
       </c>
       <c r="O6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="Q6" t="n">
         <v>1.26551960994157</v>
@@ -2220,10 +2277,10 @@
         <v>0.704654629061883</v>
       </c>
       <c r="X6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Y6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z6" t="n">
         <v>62</v>
@@ -2232,7 +2289,7 @@
         <v>2.26655532256648</v>
       </c>
       <c r="AB6" t="n">
-        <v>0.0026095209305864</v>
+        <v>0.00807520956355155</v>
       </c>
       <c r="AC6" t="n">
         <v>1.01589978521503</v>
@@ -2241,10 +2298,10 @@
         <v>0.343466368449842</v>
       </c>
       <c r="AE6" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AF6" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG6" t="n">
         <v>0.320860486165164</v>
@@ -2268,10 +2325,10 @@
         <v>1.22995859003021</v>
       </c>
       <c r="AN6" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AO6" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AP6" t="n">
         <v>62</v>
@@ -2280,7 +2337,7 @@
         <v>2.26655532256648</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.00671019667865075</v>
+        <v>0.0164996173784996</v>
       </c>
       <c r="AS6" t="n">
         <v>1.07045393016403</v>
@@ -2312,57 +2369,57 @@
       <c r="BB6" t="n">
         <v>1.40029850566019</v>
       </c>
-      <c r="BC6" t="n">
+      <c r="BC6" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD6" t="n">
+        <v>1.14395825018492</v>
+      </c>
+      <c r="BE6" t="n">
+        <v>0.559873746783635</v>
+      </c>
+      <c r="BF6" t="n">
         <v>0.002575631048371</v>
       </c>
-      <c r="BD6" t="n">
+      <c r="BG6" t="n">
         <v>0.00662305126723971</v>
       </c>
-      <c r="BE6" t="n">
-        <v>0.0197569479802072</v>
-      </c>
-      <c r="BF6" t="n">
-        <v>0.0265432020088171</v>
-      </c>
-      <c r="BG6" t="n">
-        <v>0.0150331803556572</v>
-      </c>
       <c r="BH6" t="n">
-        <v>0.0201968817964669</v>
+        <v>0.0106126243084899</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.012616242659388</v>
+        <v>0.0216841729114005</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0169497575149702</v>
+        <v>0.00807520956355156</v>
       </c>
       <c r="BK6" t="n">
+        <v>0.0164996173784996</v>
+      </c>
+      <c r="BL6" t="n">
+        <v>0.00677692949654788</v>
+      </c>
+      <c r="BM6" t="n">
+        <v>0.013846915403757</v>
+      </c>
+      <c r="BN6" t="n">
         <v>0.0285957339784935</v>
       </c>
-      <c r="BL6" t="n">
+      <c r="BO6" t="n">
         <v>0.0729731986678485</v>
       </c>
-      <c r="BM6" t="n">
+      <c r="BP6" t="n">
         <v>0.0215014657371619</v>
       </c>
-      <c r="BN6" t="n">
+      <c r="BQ6" t="n">
         <v>0.0548693987735338</v>
       </c>
-      <c r="BO6" t="n">
+      <c r="BR6" t="n">
         <v>0.017958025516122</v>
       </c>
-      <c r="BP6" t="n">
+      <c r="BS6" t="n">
         <v>0.0458269252559085</v>
       </c>
-      <c r="BQ6" t="b">
-        <v>0</v>
-      </c>
-      <c r="BR6" t="b">
-        <v>0</v>
-      </c>
-      <c r="BS6" t="b">
-        <v>0</v>
-      </c>
       <c r="BT6" t="b">
         <v>0</v>
       </c>
@@ -2408,31 +2465,40 @@
       <c r="CH6" t="b">
         <v>0</v>
       </c>
-      <c r="CI6" t="n">
+      <c r="CI6" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ6" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK6" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL6" t="n">
         <v>0.990407805013714</v>
       </c>
-      <c r="CJ6" t="n">
+      <c r="CM6" t="n">
         <v>0.999795764899988</v>
       </c>
-      <c r="CK6" t="n">
+      <c r="CN6" t="n">
         <v>0.00914353822210358</v>
       </c>
-      <c r="CL6" t="n">
+      <c r="CO6" t="n">
         <v>37.5638358047814</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B7" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C7" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="D7" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E7"/>
       <c r="F7"/>
@@ -2441,16 +2507,16 @@
       </c>
       <c r="H7"/>
       <c r="I7" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="J7" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="K7" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="L7" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="M7" t="n">
         <v>600</v>
@@ -2459,10 +2525,10 @@
         <v>1.29958847440573</v>
       </c>
       <c r="O7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q7" t="n">
         <v>1.27853805096221</v>
@@ -2486,10 +2552,10 @@
         <v>0.971891773133964</v>
       </c>
       <c r="X7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="Y7" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z7" t="n">
         <v>117</v>
@@ -2498,7 +2564,7 @@
         <v>2.26099319489918</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.00136911352632303</v>
+        <v>0.00426299148244874</v>
       </c>
       <c r="AC7" t="n">
         <v>1.0164644481466</v>
@@ -2507,10 +2573,10 @@
         <v>0.384363569211378</v>
       </c>
       <c r="AE7" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AF7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AG7" t="n">
         <v>0.358270947361978</v>
@@ -2534,10 +2600,10 @@
         <v>1.14932531698564</v>
       </c>
       <c r="AN7" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AO7" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="AP7" t="n">
         <v>117</v>
@@ -2546,7 +2612,7 @@
         <v>2.26099319489918</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.00352057763911637</v>
+        <v>0.00871032854251671</v>
       </c>
       <c r="AS7" t="n">
         <v>1.07282929872356</v>
@@ -2578,57 +2644,57 @@
       <c r="BB7" t="n">
         <v>1.40029850566019</v>
       </c>
-      <c r="BC7" t="n">
+      <c r="BC7" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD7" t="n">
+        <v>1.14395825018492</v>
+      </c>
+      <c r="BE7" t="n">
+        <v>0.559873746783635</v>
+      </c>
+      <c r="BF7" t="n">
         <v>0.00135970381136549</v>
       </c>
-      <c r="BD7" t="n">
+      <c r="BG7" t="n">
         <v>0.00349638122922554</v>
       </c>
-      <c r="BE7" t="n">
-        <v>0.0104299090068151</v>
-      </c>
-      <c r="BF7" t="n">
-        <v>0.0140124467594297</v>
-      </c>
-      <c r="BG7" t="n">
-        <v>0.0079361803933292</v>
-      </c>
       <c r="BH7" t="n">
-        <v>0.010662154881897</v>
+        <v>0.00560252048909342</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.00666025253886083</v>
+        <v>0.0114473121344717</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.00894796244570899</v>
+        <v>0.00426299148244874</v>
       </c>
       <c r="BK7" t="n">
+        <v>0.0087103285425167</v>
+      </c>
+      <c r="BL7" t="n">
+        <v>0.00357761523011585</v>
+      </c>
+      <c r="BM7" t="n">
+        <v>0.00730993814585817</v>
+      </c>
+      <c r="BN7" t="n">
         <v>0.0213858181194263</v>
       </c>
-      <c r="BL7" t="n">
+      <c r="BO7" t="n">
         <v>0.0337810627391999</v>
       </c>
-      <c r="BM7" t="n">
+      <c r="BP7" t="n">
         <v>0.0161729734586813</v>
       </c>
-      <c r="BN7" t="n">
+      <c r="BQ7" t="n">
         <v>0.0255468473563257</v>
       </c>
-      <c r="BO7" t="n">
+      <c r="BR7" t="n">
         <v>0.013539031611834</v>
       </c>
-      <c r="BP7" t="n">
+      <c r="BS7" t="n">
         <v>0.0213862698052182</v>
       </c>
-      <c r="BQ7" t="b">
-        <v>0</v>
-      </c>
-      <c r="BR7" t="b">
-        <v>0</v>
-      </c>
-      <c r="BS7" t="b">
-        <v>0</v>
-      </c>
       <c r="BT7" t="b">
         <v>0</v>
       </c>
@@ -2674,31 +2740,40 @@
       <c r="CH7" t="b">
         <v>0</v>
       </c>
-      <c r="CI7" t="n">
+      <c r="CI7" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ7" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK7" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL7" t="n">
         <v>0.998122550225431</v>
       </c>
-      <c r="CJ7" t="n">
+      <c r="CM7" t="n">
         <v>0.999894443336438</v>
       </c>
-      <c r="CK7" t="n">
+      <c r="CN7" t="n">
         <v>0.00429906268465443</v>
       </c>
-      <c r="CL7" t="n">
+      <c r="CO7" t="n">
         <v>89.4063653882903</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B8" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C8" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="D8" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E8" t="n">
         <v>11.4</v>
@@ -2711,16 +2786,16 @@
       </c>
       <c r="H8"/>
       <c r="I8" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="J8" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="K8" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="L8" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="M8" t="n">
         <v>600</v>
@@ -2729,10 +2804,10 @@
         <v>1.06700748829</v>
       </c>
       <c r="O8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P8" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q8" t="n">
         <v>0.906185406866212</v>
@@ -2756,10 +2831,10 @@
         <v>1.1228647114697</v>
       </c>
       <c r="X8" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Y8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z8" t="n">
         <v>166</v>
@@ -2768,7 +2843,7 @@
         <v>2.26751588714622</v>
       </c>
       <c r="AB8" t="n">
-        <v>0.000965487299879778</v>
+        <v>0.00301237119151321</v>
       </c>
       <c r="AC8" t="n">
         <v>1.17747149778095</v>
@@ -2777,10 +2852,10 @@
         <v>0.0327494414017846</v>
       </c>
       <c r="AE8" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AF8" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG8" t="n">
         <v>0.0326813688912162</v>
@@ -2804,10 +2879,10 @@
         <v>1.38367415839523</v>
       </c>
       <c r="AN8" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AO8" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AP8" t="n">
         <v>166</v>
@@ -2816,7 +2891,7 @@
         <v>2.26751588714622</v>
       </c>
       <c r="AR8" t="n">
-        <v>0.00248268162826229</v>
+        <v>0.00615500708319985</v>
       </c>
       <c r="AS8" t="n">
         <v>1.00208291491079</v>
@@ -2848,57 +2923,57 @@
       <c r="BB8" t="n">
         <v>1.40029850566019</v>
       </c>
-      <c r="BC8" t="n">
+      <c r="BC8" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD8" t="n">
+        <v>1.14395825018492</v>
+      </c>
+      <c r="BE8" t="n">
+        <v>0.559873746783635</v>
+      </c>
+      <c r="BF8" t="n">
         <v>0.000960811816587381</v>
       </c>
-      <c r="BD8" t="n">
+      <c r="BG8" t="n">
         <v>0.00247065895693898</v>
       </c>
-      <c r="BE8" t="n">
-        <v>0.00737011968041433</v>
-      </c>
-      <c r="BF8" t="n">
-        <v>0.009901659694725</v>
-      </c>
-      <c r="BG8" t="n">
-        <v>0.00560796832129358</v>
-      </c>
       <c r="BH8" t="n">
-        <v>0.0075342323197017</v>
+        <v>0.00395892682185542</v>
       </c>
       <c r="BI8" t="n">
-        <v>0.00470635537482765</v>
+        <v>0.00808905047925037</v>
       </c>
       <c r="BJ8" t="n">
-        <v>0.00632292708187929</v>
+        <v>0.00301237119151321</v>
       </c>
       <c r="BK8" t="n">
+        <v>0.00615500708319984</v>
+      </c>
+      <c r="BL8" t="n">
+        <v>0.00252806159662541</v>
+      </c>
+      <c r="BM8" t="n">
+        <v>0.00516544477580749</v>
+      </c>
+      <c r="BN8" t="n">
         <v>0.0119069080092765</v>
       </c>
-      <c r="BL8" t="n">
+      <c r="BO8" t="n">
         <v>0.027967771303443</v>
       </c>
-      <c r="BM8" t="n">
+      <c r="BP8" t="n">
         <v>0.00902123679389679</v>
       </c>
-      <c r="BN8" t="n">
+      <c r="BQ8" t="n">
         <v>0.0211897066248723</v>
       </c>
-      <c r="BO8" t="n">
+      <c r="BR8" t="n">
         <v>0.00755768544432677</v>
       </c>
-      <c r="BP8" t="n">
+      <c r="BS8" t="n">
         <v>0.0177520157143748</v>
       </c>
-      <c r="BQ8" t="b">
-        <v>0</v>
-      </c>
-      <c r="BR8" t="b">
-        <v>0</v>
-      </c>
-      <c r="BS8" t="b">
-        <v>0</v>
-      </c>
       <c r="BT8" t="b">
         <v>0</v>
       </c>
@@ -2944,31 +3019,40 @@
       <c r="CH8" t="b">
         <v>0</v>
       </c>
-      <c r="CI8" t="n">
+      <c r="CI8" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ8" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK8" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL8" t="n">
         <v>0.859492457974167</v>
       </c>
-      <c r="CJ8" t="n">
+      <c r="CM8" t="n">
         <v>0.999860422432155</v>
       </c>
-      <c r="CK8" t="n">
+      <c r="CN8" t="n">
         <v>0.00357716477998528</v>
       </c>
-      <c r="CL8" t="n">
+      <c r="CO8" t="n">
         <v>9.155139171956</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B9" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="C9" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="D9" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E9" t="n">
         <v>11.3</v>
@@ -2981,16 +3065,16 @@
       </c>
       <c r="H9"/>
       <c r="I9" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="J9" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="K9" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="L9" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="M9" t="n">
         <v>900</v>
@@ -2999,10 +3083,10 @@
         <v>1.2190721160156</v>
       </c>
       <c r="O9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P9" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q9" t="n">
         <v>1.06999520481712</v>
@@ -3026,10 +3110,10 @@
         <v>1.17849683682608</v>
       </c>
       <c r="X9" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Y9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z9" t="n">
         <v>192</v>
@@ -3038,7 +3122,7 @@
         <v>2.27101733017835</v>
       </c>
       <c r="AB9" t="n">
-        <v>0.000836690595328864</v>
+        <v>0.00261222311426031</v>
       </c>
       <c r="AC9" t="n">
         <v>1.13932484045474</v>
@@ -3047,10 +3131,10 @@
         <v>0.0744366757599961</v>
       </c>
       <c r="AE9" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AF9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG9" t="n">
         <v>0.0739757902704793</v>
@@ -3074,10 +3158,10 @@
         <v>1.56049523863239</v>
       </c>
       <c r="AN9" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AO9" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AP9" t="n">
         <v>192</v>
@@ -3086,7 +3170,7 @@
         <v>2.27101733017835</v>
       </c>
       <c r="AR9" t="n">
-        <v>0.00215149010227422</v>
+        <v>0.0053374072280561</v>
       </c>
       <c r="AS9" t="n">
         <v>1.00623022056043</v>
@@ -3118,57 +3202,57 @@
       <c r="BB9" t="n">
         <v>1.40029850566019</v>
       </c>
-      <c r="BC9" t="n">
+      <c r="BC9" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD9" t="n">
+        <v>1.14395825018492</v>
+      </c>
+      <c r="BE9" t="n">
+        <v>0.559873746783635</v>
+      </c>
+      <c r="BF9" t="n">
         <v>0.00083318245866082</v>
       </c>
-      <c r="BD9" t="n">
+      <c r="BG9" t="n">
         <v>0.00214246917941354</v>
       </c>
-      <c r="BE9" t="n">
-        <v>0.00639111044425175</v>
-      </c>
-      <c r="BF9" t="n">
-        <v>0.00858637355083302</v>
-      </c>
-      <c r="BG9" t="n">
-        <v>0.00486303431469344</v>
-      </c>
       <c r="BH9" t="n">
-        <v>0.00653342319471774</v>
+        <v>0.00343304310599284</v>
       </c>
       <c r="BI9" t="n">
-        <v>0.00408118704915391</v>
+        <v>0.00701454213008253</v>
       </c>
       <c r="BJ9" t="n">
-        <v>0.00548302158764526</v>
+        <v>0.00261222311426032</v>
       </c>
       <c r="BK9" t="n">
+        <v>0.00533740722805611</v>
+      </c>
+      <c r="BL9" t="n">
+        <v>0.00219224674422059</v>
+      </c>
+      <c r="BM9" t="n">
+        <v>0.00447929334765063</v>
+      </c>
+      <c r="BN9" t="n">
         <v>0.0111229984662164</v>
       </c>
-      <c r="BL9" t="n">
+      <c r="BO9" t="n">
         <v>0.0214574825391707</v>
       </c>
-      <c r="BM9" t="n">
+      <c r="BP9" t="n">
         <v>0.00843229419261486</v>
       </c>
-      <c r="BN9" t="n">
+      <c r="BQ9" t="n">
         <v>0.0162668192351851</v>
       </c>
-      <c r="BO9" t="n">
+      <c r="BR9" t="n">
         <v>0.00706598181365313</v>
       </c>
-      <c r="BP9" t="n">
+      <c r="BS9" t="n">
         <v>0.0136310529799195</v>
       </c>
-      <c r="BQ9" t="b">
-        <v>0</v>
-      </c>
-      <c r="BR9" t="b">
-        <v>0</v>
-      </c>
-      <c r="BS9" t="b">
-        <v>0</v>
-      </c>
       <c r="BT9" t="b">
         <v>0</v>
       </c>
@@ -3214,47 +3298,56 @@
       <c r="CH9" t="b">
         <v>0</v>
       </c>
-      <c r="CI9" t="n">
+      <c r="CI9" t="b">
+        <v>0</v>
+      </c>
+      <c r="CJ9" t="b">
+        <v>0</v>
+      </c>
+      <c r="CK9" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL9" t="n">
         <v>0.97052787072339</v>
       </c>
-      <c r="CJ9" t="n">
+      <c r="CM9" t="n">
         <v>0.9999173464781</v>
       </c>
-      <c r="CK9" t="n">
+      <c r="CN9" t="n">
         <v>0.00274889511230893</v>
       </c>
-      <c r="CL9" t="n">
+      <c r="CO9" t="n">
         <v>27.0787617274612</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="s">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="B10" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="C10" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="D10" t="s">
-        <v>93</v>
+        <v>96</v>
       </c>
       <c r="E10"/>
       <c r="F10"/>
       <c r="G10"/>
       <c r="H10"/>
       <c r="I10" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="J10" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="K10" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="L10" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="M10" t="n">
         <v>300</v>
@@ -3263,10 +3356,10 @@
         <v>1.29592767022994</v>
       </c>
       <c r="O10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="P10" t="s">
-        <v>99</v>
+        <v>102</v>
       </c>
       <c r="Q10" t="n">
         <v>1.21830830268424</v>
@@ -3290,10 +3383,10 @@
         <v>1.13993468094949</v>
       </c>
       <c r="X10" t="s">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="Y10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="Z10" t="n">
         <v>70</v>
@@ -3302,7 +3395,7 @@
         <v>2.24707891382181</v>
       </c>
       <c r="AB10" t="n">
-        <v>0.00137736886136188</v>
+        <v>0.00428833469847012</v>
       </c>
       <c r="AC10" t="n">
         <v>1.06371077614318</v>
@@ -3311,10 +3404,10 @@
         <v>0.00933095135088507</v>
       </c>
       <c r="AE10" t="s">
-        <v>98</v>
+        <v>101</v>
       </c>
       <c r="AF10" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="AG10" t="n">
         <v>0.00933809045098793</v>
@@ -3338,10 +3431,10 @@
         <v>3.7919252851978</v>
       </c>
       <c r="AN10" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="AO10" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="AP10" t="n">
         <v>70</v>
@@ -3350,7 +3443,7 @@
         <v>2.24707891382181</v>
       </c>
       <c r="AR10" t="n">
-        <v>0.00354180564350198</v>
+        <v>0.00876211089741444</v>
       </c>
       <c r="AS10" t="n">
         <v>0.999235486083549</v>
@@ -3382,57 +3475,57 @@
       <c r="BB10" t="n">
         <v>1.40029850566019</v>
       </c>
-      <c r="BC10" t="n">
+      <c r="BC10" t="s">
+        <v>106</v>
+      </c>
+      <c r="BD10" t="n">
+        <v>1.14395825018492</v>
+      </c>
+      <c r="BE10" t="n">
+        <v>0.559873746783635</v>
+      </c>
+      <c r="BF10" t="n">
         <v>0.00136778716493501</v>
       </c>
-      <c r="BD10" t="n">
+      <c r="BG10" t="n">
         <v>0.00351716699554718</v>
       </c>
-      <c r="BE10" t="n">
-        <v>0.010491914159331</v>
-      </c>
-      <c r="BF10" t="n">
-        <v>0.0140957498733754</v>
-      </c>
-      <c r="BG10" t="n">
-        <v>0.00798336048621017</v>
-      </c>
       <c r="BH10" t="n">
-        <v>0.010725540721521</v>
+        <v>0.00563582712074019</v>
       </c>
       <c r="BI10" t="n">
-        <v>0.0066998473209626</v>
+        <v>0.0115153656845392</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0090011575192029</v>
+        <v>0.00428833469847011</v>
       </c>
       <c r="BK10" t="n">
+        <v>0.00876211089741443</v>
+      </c>
+      <c r="BL10" t="n">
+        <v>0.00359888392745936</v>
+      </c>
+      <c r="BM10" t="n">
+        <v>0.0073533952679979</v>
+      </c>
+      <c r="BN10" t="n">
         <v>0.308237546966081</v>
       </c>
-      <c r="BL10" t="n">
+      <c r="BO10" t="n">
         <v>0.0750587500532054</v>
       </c>
-      <c r="BM10" t="n">
+      <c r="BP10" t="n">
         <v>0.23209795441895</v>
       </c>
-      <c r="BN10" t="n">
+      <c r="BQ10" t="n">
         <v>0.0565180411019468</v>
       </c>
-      <c r="BO10" t="n">
+      <c r="BR10" t="n">
         <v>0.193959479459962</v>
       </c>
-      <c r="BP10" t="n">
+      <c r="BS10" t="n">
         <v>0.0472309627186241</v>
       </c>
-      <c r="BQ10" t="b">
-        <v>0</v>
-      </c>
-      <c r="BR10" t="b">
-        <v>0</v>
-      </c>
-      <c r="BS10" t="b">
-        <v>0</v>
-      </c>
       <c r="BT10" t="b">
         <v>0</v>
       </c>
@@ -3455,10 +3548,10 @@
         <v>0</v>
       </c>
       <c r="CA10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CB10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CC10" t="b">
         <v>0</v>
@@ -3467,27 +3560,36 @@
         <v>1</v>
       </c>
       <c r="CE10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CF10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG10" t="b">
         <v>1</v>
       </c>
       <c r="CH10" t="b">
-        <v>0</v>
-      </c>
-      <c r="CI10" t="n">
+        <v>1</v>
+      </c>
+      <c r="CI10" t="b">
+        <v>1</v>
+      </c>
+      <c r="CJ10" t="b">
+        <v>1</v>
+      </c>
+      <c r="CK10" t="b">
+        <v>0</v>
+      </c>
+      <c r="CL10" t="n">
         <v>0.0305018423219471</v>
       </c>
-      <c r="CJ10" t="n">
+      <c r="CM10" t="n">
         <v>0.999884540341955</v>
       </c>
-      <c r="CK10" t="n">
+      <c r="CN10" t="n">
         <v>0.00944106256792635</v>
       </c>
-      <c r="CL10" t="n">
+      <c r="CO10" t="n">
         <v>0.988336988951291</v>
       </c>
     </row>
